--- a/data/watchlist_signals_2026-10-20.xlsx
+++ b/data/watchlist_signals_2026-10-20.xlsx
@@ -11,16 +11,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correlation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News &amp; Sentiment" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Score History" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Firm Targets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News &amp; Sentiment" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Score History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Signals'!$A$1:$AQ$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Backtest'!$A$1:$P$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'News &amp; Sentiment'!$A$1:$I$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'History'!$A$1:$I$937</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'News &amp; Sentiment'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'History'!$A$1:$I$937</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,10 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="+0.0;-0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +115,16 @@
     <font>
       <name val="Aptos"/>
       <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F7A33"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00B02A17"/>
       <sz val="10"/>
     </font>
     <font>
@@ -272,23 +284,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,7 +309,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -305,13 +317,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="23" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="25" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -322,30 +334,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16090,6 +16106,3426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>Firms</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>PT med</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>PT ups %</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>PT high</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>PT low</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="n">
+        <v>531.87</v>
+      </c>
+      <c r="D2" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="26" t="n">
+        <v>612.5</v>
+      </c>
+      <c r="F2" s="37" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>625</v>
+      </c>
+      <c r="H2" s="26" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="n">
+        <v>289.08</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="F3" s="38" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G3" s="30" t="n">
+        <v>310</v>
+      </c>
+      <c r="H3" s="30" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>896.0700000000001</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F4" s="37" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Sandisk</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>1365.38</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>2175</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>430</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>430</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>676</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>740</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>315</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>1283.66</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>1430</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>262.63</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>461.56</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>570</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>570</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>SK hynix</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>139.79</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>1630.84</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Seagate</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>675.13</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>960</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>960</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>694.25</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>800</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>800</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>111.67</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>140</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>181.19</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>225</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>225</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>131.14</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>240</v>
+      </c>
+      <c r="F18" s="37" t="n">
+        <v>83</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>240</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>241.92</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>259</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>280</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>319.61</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>490</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>490</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="F21" s="38" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>ALNY</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Alnylam</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>230.71</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="F22" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>375</v>
+      </c>
+      <c r="H22" s="26" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Vistra</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="F23" s="39" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>181</v>
+      </c>
+      <c r="H23" s="30" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>230</v>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>230</v>
+      </c>
+      <c r="H24" s="26" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Marvell</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>240.42</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="F25" s="39" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" s="30" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>365</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>370</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>First Solar</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>174.43</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <v>323</v>
+      </c>
+      <c r="H27" s="30" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>291.69</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>380</v>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>284.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>BIDU</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Baidu</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="D29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>166</v>
+      </c>
+      <c r="F29" s="39" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>166</v>
+      </c>
+      <c r="H29" s="30" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Super Micro</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="F31" s="39" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>129</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>175.71</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="F32" s="37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Lumentum Holdings</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>822.51</v>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>1010.3</v>
+      </c>
+      <c r="F33" s="39" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <v>820.59</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>155.65</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="26" t="n">
+        <v>142</v>
+      </c>
+      <c r="F34" s="40" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>142</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>534.74</v>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>700</v>
+      </c>
+      <c r="F35" s="39" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G35" s="30" t="n">
+        <v>700</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="F36" s="37" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G36" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="F37" s="39" t="n">
+        <v>65</v>
+      </c>
+      <c r="G37" s="30" t="n">
+        <v>106</v>
+      </c>
+      <c r="H37" s="30" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>221.06</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="26" t="n">
+        <v>160</v>
+      </c>
+      <c r="F38" s="40" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="G38" s="26" t="n">
+        <v>160</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F39" s="39" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>130</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="26" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F40" s="37" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>110</v>
+      </c>
+      <c r="H40" s="26" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>460</v>
+      </c>
+      <c r="F41" s="39" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G41" s="30" t="n">
+        <v>460</v>
+      </c>
+      <c r="H41" s="30" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="n"/>
+      <c r="E42" s="1" t="n"/>
+      <c r="F42" s="1" t="n"/>
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>Per-firm detail (latest report per firm, sell-side research)</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+      <c r="H43" s="1" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Firm</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Report title</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n"/>
+      <c r="H44" s="1" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>625</v>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="inlineStr">
+        <is>
+          <t>Microsoft: Segment Reset Better Highlights Returns; Microsoft Cloud ROIC Stabilizing in the Low-30s Despite Capital Intensity; Reiterate OW</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n"/>
+      <c r="H45" s="1" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr"/>
+      <c r="D46" s="30" t="n">
+        <v>600</v>
+      </c>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="inlineStr">
+        <is>
+          <t>Software Trends: AI 3.0: the rising value of the interface layer</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="n"/>
+      <c r="H46" s="1" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="inlineStr"/>
+      <c r="D47" s="30" t="n">
+        <v>310</v>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="inlineStr">
+        <is>
+          <t>UEGW IBD conference: takeaways for ABBV and GILD</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n"/>
+      <c r="H47" s="1" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="inlineStr"/>
+      <c r="D48" s="30" t="n">
+        <v>289</v>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="inlineStr">
+        <is>
+          <t>US Biopharmaceuticals: Pharma medical meeting updates: TL1a expands use case, eloraTZP goes to Ph3</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n"/>
+      <c r="H48" s="1" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Guggenheim</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>288</v>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="inlineStr">
+        <is>
+          <t>ABBV: Previewing3Q 2026 Results; Expecting an In-Line Quarter; Reiterate Buy Rating, $288 Price Target</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="n"/>
+      <c r="H49" s="1" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr"/>
+      <c r="D50" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="inlineStr">
+        <is>
+          <t>APGE: Acquired by ABBV, Drop Coverage</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="n"/>
+      <c r="H50" s="1" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="inlineStr">
+        <is>
+          <t>Sandisk Corp (SNDK.O): MU Read-Thru: NAND Now Tight Thru CY28; Reit. Buy on S/D Fundamentals</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n"/>
+      <c r="H51" s="1" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr"/>
+      <c r="D52" s="30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="inlineStr">
+        <is>
+          <t>Micron Technology Inc. (MU): First Take: Strong results and mixed should move the stock modestly higher</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n"/>
+      <c r="H52" s="1" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="inlineStr"/>
+      <c r="D53" s="30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="inlineStr">
+        <is>
+          <t>IT Hardware Industry Expert Call Series Takeaways: Dive into HBF and Toshiba news with Tom Coughlin: Industry Overview</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n"/>
+      <c r="H53" s="1" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>ASIA TECHNOLOGY TRACKER: Asia Pacific Reports/Notes</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n"/>
+      <c r="H54" s="1" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="inlineStr"/>
+      <c r="D55" s="30" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="inlineStr">
+        <is>
+          <t>North America Connectors &amp; Other Components, Electronic Components &amp; Equipment and Hardware &amp; Storage: 3Q26 Earnings Preview – Durable AI Demand; Most Bullish On Connectivity</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>Wedbush</t>
+        </is>
+      </c>
+      <c r="C56" s="27" t="inlineStr"/>
+      <c r="D56" s="30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="inlineStr">
+        <is>
+          <t>Aug2026 Investor Day Recap</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="n"/>
+      <c r="H56" s="1" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>430</v>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="inlineStr">
+        <is>
+          <t>Alphabet3Q Preview: Cloud strength to highlight the quarter; Reit Buy</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="n"/>
+      <c r="H57" s="1" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr"/>
+      <c r="D58" s="30" t="n">
+        <v>740</v>
+      </c>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="inlineStr">
+        <is>
+          <t>North America Connectors &amp; Other Components, Electronic Components &amp; Equipment and Hardware &amp; Storage: 3Q26 Earnings Preview – Durable AI Demand; Most Bullish On Connectivity</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="n"/>
+      <c r="H58" s="1" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr"/>
+      <c r="D59" s="30" t="n">
+        <v>720</v>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="inlineStr">
+        <is>
+          <t>IT Hardware Industry Expert Call Series Takeaways: HDD LTA dynamics &amp; thoughts on Toshiba: Industry Overview</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n"/>
+      <c r="H59" s="1" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr"/>
+      <c r="D60" s="30" t="n">
+        <v>676</v>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="inlineStr">
+        <is>
+          <t>F1Q27 Preview – The Cycle Isn‘t Over, But The Market Is Pricing HDDs Like It Is: Hard Disk Drives | North America</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="n"/>
+      <c r="H60" s="1" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="n">
+        <v>615</v>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="inlineStr">
+        <is>
+          <t>Global Technology: Reported HDD capacity additions by Toshiba:: Framing implications for the HDD supply chain</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="n"/>
+      <c r="H61" s="1" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="inlineStr"/>
+      <c r="D62" s="30" t="n">
+        <v>600</v>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="inlineStr">
+        <is>
+          <t>Hardware &amp; Networking: HDD Preview: Recent Pullback Creates Positive Setup into F1Q27as Industry Trends Stay Intact; Favor STX vs. WDC</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="n"/>
+      <c r="H62" s="1" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="inlineStr"/>
+      <c r="D63" s="30" t="n">
+        <v>315</v>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="inlineStr">
+        <is>
+          <t>Asia Electrical Equipment: Key Takeaways from LS Electric and Sieyuan at Data Center World Asia2026in Singapore</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="n"/>
+      <c r="H63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="C64" s="27" t="inlineStr"/>
+      <c r="D64" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp: Ripping Off The Gross Margin Band-Aid, And Still Guiding Up Nicely</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="n"/>
+      <c r="H64" s="1" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C65" s="27" t="inlineStr"/>
+      <c r="D65" s="30" t="n">
+        <v>1430</v>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="inlineStr">
+        <is>
+          <t>Mounjaro+Zepbound+Foundayo Script Tracker: Eli Lilly &amp; Co. | North America</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="n"/>
+      <c r="H65" s="1" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr"/>
+      <c r="D66" s="30" t="n">
+        <v>350</v>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="inlineStr">
+        <is>
+          <t>Amazon to Top Pick and5 Catalysts to Deliver Outperformance: None</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="n"/>
+      <c r="H66" s="1" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>Wolfe Research</t>
+        </is>
+      </c>
+      <c r="C67" s="27" t="inlineStr"/>
+      <c r="D67" s="30" t="n">
+        <v>320</v>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="inlineStr">
+        <is>
+          <t>Internet Large Cap Q3 Preview: Trading Calls (AMZN, APP, DASH) + Setups + Key Themes</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="n"/>
+      <c r="H67" s="1" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C68" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="n">
+        <v>570</v>
+      </c>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="inlineStr">
+        <is>
+          <t>Dell Technologies Inc. (DELL): F2Q27review: Enterprise refresh and AI demand drive beat &amp; raise</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="n"/>
+      <c r="H68" s="1" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C69" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="n">
+        <v>245</v>
+      </c>
+      <c r="E69" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="inlineStr">
+        <is>
+          <t>SK hynix ADR</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="n"/>
+      <c r="H69" s="1" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C70" s="27" t="inlineStr"/>
+      <c r="D70" s="30" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="inlineStr">
+        <is>
+          <t>ASML: 3Q26 First Take: Key points include the very strong gross margin and ‘26guidance outgrowing WFE.</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="n"/>
+      <c r="H70" s="1" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C71" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D71" s="30" t="n">
+        <v>960</v>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="inlineStr">
+        <is>
+          <t>Americas Technology: Semiconductors: 3Q Preview: Expect stocks to work on better numbers following sector-wide pullback: None</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="n"/>
+      <c r="H71" s="1" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C72" s="27" t="inlineStr"/>
+      <c r="D72" s="30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc (META.O): Meta Enterprise Announced; Suggests Significant Infrastructure Capacity into ‘27</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="n"/>
+      <c r="H72" s="1" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="inlineStr"/>
+      <c r="D73" s="30" t="n">
+        <v>140</v>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="inlineStr">
+        <is>
+          <t>Walt Disney Co (DIS.N): Deconstructing FY27 Guidance</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="n"/>
+      <c r="H73" s="1" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C74" s="27" t="inlineStr"/>
+      <c r="D74" s="30" t="n">
+        <v>125</v>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="inlineStr">
+        <is>
+          <t>Walt Disney Co.: Eyes toward FY27</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="n"/>
+      <c r="H74" s="1" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C75" s="27" t="inlineStr"/>
+      <c r="D75" s="30" t="n">
+        <v>225</v>
+      </c>
+      <c r="E75" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="inlineStr">
+        <is>
+          <t>3Q26E preview on ANET, CLS, FFIV &amp; industry networking model update: AMERICAS TECHNOLOGY: HARDWARE</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="n"/>
+      <c r="H75" s="1" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C76" s="27" t="inlineStr"/>
+      <c r="D76" s="30" t="n">
+        <v>240</v>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="inlineStr">
+        <is>
+          <t>Oracle Corporation: Our2026 Oracle Investor Day Wish List</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="n"/>
+      <c r="H76" s="1" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr"/>
+      <c r="D77" s="30" t="n">
+        <v>280</v>
+      </c>
+      <c r="E77" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="inlineStr">
+        <is>
+          <t>Transcript</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="n"/>
+      <c r="H77" s="1" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C78" s="27" t="inlineStr">
+        <is>
+          <t>Equal-Weight</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="n">
+        <v>238</v>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="inlineStr">
+        <is>
+          <t>3Q26 Earnings Preview: – A Relatively Clear3Q Setup, But Cloudier Beyond</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="n"/>
+      <c r="H78" s="1" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C79" s="27" t="inlineStr"/>
+      <c r="D79" s="30" t="n">
+        <v>490</v>
+      </c>
+      <c r="E79" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="inlineStr">
+        <is>
+          <t>Snowflake Inc (SNOW.N): Takeaways From F‘2Q27 Callback with Management</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="n"/>
+      <c r="H79" s="1" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C80" s="27" t="inlineStr"/>
+      <c r="D80" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp (NVDA.O): Preview – Investor Focus on AI Financing &amp; Rubin Ramp</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="n"/>
+      <c r="H80" s="1" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C81" s="27" t="inlineStr"/>
+      <c r="D81" s="30" t="n">
+        <v>115</v>
+      </c>
+      <c r="E81" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="inlineStr">
+        <is>
+          <t>Broadcom Inc: Stronger AI ramp, but in more competitive neighborhood</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="n"/>
+      <c r="H81" s="1" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>ALNY</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C82" s="27" t="inlineStr"/>
+      <c r="D82" s="30" t="n">
+        <v>375</v>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals: Adjusting Amvuttra Estimates Based on July/Aug Symphony Data</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="n"/>
+      <c r="H82" s="1" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>ALNY</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C83" s="27" t="inlineStr"/>
+      <c r="D83" s="30" t="n">
+        <v>340</v>
+      </c>
+      <c r="E83" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals Inc (ALNY.O): Amvuttra Unscathed, TRITON-CM Recouping Confidence Post CARDIO-TTRansform ESC Pubs</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="n"/>
+      <c r="H83" s="1" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>Bernstein</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>Outperform</t>
+        </is>
+      </c>
+      <c r="D84" s="30" t="n">
+        <v>181</v>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="inlineStr">
+        <is>
+          <t>Vistra (VST): Looking past the ERCOT noise...</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="n"/>
+      <c r="H84" s="1" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="C85" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D85" s="30" t="n">
+        <v>170</v>
+      </c>
+      <c r="E85" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="inlineStr">
+        <is>
+          <t>Harvesting Power Cash Flows While They Shine: Buy on Diverse &amp; Durable Profile</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="n"/>
+      <c r="H85" s="1" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D86" s="30" t="n">
+        <v>230</v>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="inlineStr">
+        <is>
+          <t>Palantir Technologies (PLTR): Upgrade to Buy: Moat likely compounds into another step function change in TAM</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="n"/>
+      <c r="H86" s="1" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="inlineStr"/>
+      <c r="D87" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="E87" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="inlineStr">
+        <is>
+          <t>Investor day calls for $30 EPS in CY30</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="n"/>
+      <c r="H87" s="1" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="inlineStr"/>
+      <c r="D88" s="30" t="n">
+        <v>370</v>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="inlineStr">
+        <is>
+          <t>Apple Inc.: iPhone Duo lead times extend to next year; Pro and Pro Max broadly stabilize</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="n"/>
+      <c r="H88" s="1" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="inlineStr"/>
+      <c r="D89" s="30" t="n">
+        <v>365</v>
+      </c>
+      <c r="E89" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="inlineStr">
+        <is>
+          <t>North America Hardware &amp; Storage: 3Q PC Prelim Results: 1H Pull-In Causes Missed3Q Seasonal Bounce; Supply Constraints &amp; Weak Demand Remain</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="n"/>
+      <c r="H89" s="1" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C90" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="n">
+        <v>360</v>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F90" s="27" t="inlineStr">
+        <is>
+          <t>iPhone18 Launch Preview – Ternus, Foldables, and Pricing</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="n"/>
+      <c r="H90" s="1" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C91" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D91" s="30" t="n">
+        <v>323</v>
+      </c>
+      <c r="E91" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F91" s="27" t="inlineStr">
+        <is>
+          <t>Taking Action Against Stockpiling; Increases Our Confidence in Price Increases Ahead</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n"/>
+      <c r="H91" s="1" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr"/>
+      <c r="D92" s="30" t="n">
+        <v>252</v>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F92" s="27" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Power Infrastructure: Into the3Q Print: Expect Upbeat Tone Despite Weak Macro Investor Sentiment; Top Picks are AGX, INIO, and NXT</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="n"/>
+      <c r="H92" s="1" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C93" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D93" s="30" t="n">
+        <v>400</v>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F93" s="27" t="inlineStr">
+        <is>
+          <t>Rubrik, Inc. (RBRK.N): F2Q27 Review: Clean Results Against Consistently Robust Execution; Buy Weakness</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="n"/>
+      <c r="H93" s="1" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C94" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="n">
+        <v>380</v>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F94" s="27" t="inlineStr">
+        <is>
+          <t>NET: Clef Strikes the Right Tune; Moves NET Into the Model Layer</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="n"/>
+      <c r="H94" s="1" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C95" s="27" t="inlineStr"/>
+      <c r="D95" s="30" t="n">
+        <v>284.43</v>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F95" s="27" t="inlineStr">
+        <is>
+          <t>2Q26 Results – Execution + More Consumption Equals Acceleration in2Q, Reiterate OW</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="n"/>
+      <c r="H95" s="1" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="inlineStr">
+        <is>
+          <t>BIDU</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C96" s="27" t="inlineStr"/>
+      <c r="D96" s="30" t="n">
+        <v>166</v>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F96" s="27" t="inlineStr">
+        <is>
+          <t>Baidu.com (BIDU.O): Citi Global TMT Conference Takeaways: Strong GPU Demand &amp; Value Unlocking</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="n"/>
+      <c r="H96" s="1" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C97" s="27" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="D97" s="30" t="n">
+        <v>34</v>
+      </c>
+      <c r="E97" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F97" s="27" t="inlineStr">
+        <is>
+          <t>Americas Technology: Hardware: Server2Q26market share and outlook update</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="n"/>
+      <c r="H97" s="1" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>Bernstein</t>
+        </is>
+      </c>
+      <c r="C98" s="27" t="inlineStr"/>
+      <c r="D98" s="30" t="n">
+        <v>129</v>
+      </c>
+      <c r="E98" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F98" s="27" t="inlineStr">
+        <is>
+          <t>Global Media: What Happens When AI meets proven IP? An evergreen pipeline for big media</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="n"/>
+      <c r="H98" s="1" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C99" s="27" t="inlineStr"/>
+      <c r="D99" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="E99" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F99" s="27" t="inlineStr">
+        <is>
+          <t>Netflix Inc: NFLX Trending &amp; 3Q Preview, 10/6/26: NFLX Story &amp; Market’s Positioning Unchanged Through3Q; Focus on Content Slate, Engagement, 2027 Revenue Growth &amp; Margin Expansion;</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="n"/>
+      <c r="H99" s="1" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C100" s="27" t="inlineStr"/>
+      <c r="D100" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="E100" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F100" s="27" t="inlineStr">
+        <is>
+          <t>3Q26 Media Preview</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="n"/>
+      <c r="H100" s="1" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C101" s="27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D101" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="E101" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F101" s="27" t="inlineStr">
+        <is>
+          <t>Americas Technology: Semiconductors: 3Q Preview: Expect stocks to work on better numbers following sector-wide pullback: None</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="n"/>
+      <c r="H101" s="1" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C102" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D102" s="30" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F102" s="27" t="inlineStr">
+        <is>
+          <t>Citi‘s Most Read - North America</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="n"/>
+      <c r="H102" s="1" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="inlineStr">
+        <is>
+          <t>Equal-Weight</t>
+        </is>
+      </c>
+      <c r="D103" s="30" t="n">
+        <v>820.59</v>
+      </c>
+      <c r="E103" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F103" s="27" t="inlineStr">
+        <is>
+          <t>Easily Clearing a Challenging Bar</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="n"/>
+      <c r="H103" s="1" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C104" s="27" t="inlineStr"/>
+      <c r="D104" s="30" t="n">
+        <v>142</v>
+      </c>
+      <c r="E104" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F104" s="27" t="inlineStr">
+        <is>
+          <t>RDDT: 3Q:26 EPS Preview: Similar Setup to2Q, Strong Ad Revs and US DAU Weakness</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="n"/>
+      <c r="H104" s="1" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D105" s="30" t="n">
+        <v>700</v>
+      </c>
+      <c r="E105" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F105" s="27" t="inlineStr">
+        <is>
+          <t>Americas Technology: Semiconductors: 3Q Preview: Expect stocks to work on better numbers following sector-wide pullback: None</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="n"/>
+      <c r="H105" s="1" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C106" s="27" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="D106" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="E106" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F106" s="27" t="inlineStr">
+        <is>
+          <t>Elon Goes Low (Band)...: Implications Across the Telco Ecosystem</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="n"/>
+      <c r="H106" s="1" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C107" s="27" t="inlineStr"/>
+      <c r="D107" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="E107" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F107" s="27" t="inlineStr">
+        <is>
+          <t>Space Exploration Technologies (SPCX.O): 3Q26 Likely Another Strong Q Along Multi-Year Catalyst-Rich Arc</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="n"/>
+      <c r="H107" s="1" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D108" s="30" t="n">
+        <v>106</v>
+      </c>
+      <c r="E108" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F108" s="27" t="inlineStr">
+        <is>
+          <t>Research Unplugged: Discussion of our upgrade of CoreWeave (CRWV) to Buy</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="n"/>
+      <c r="H108" s="1" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr"/>
+      <c r="D109" s="30" t="n">
+        <v>99</v>
+      </c>
+      <c r="E109" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F109" s="27" t="inlineStr">
+        <is>
+          <t>Fully Connected Conference Takeaways: Showcasing the Breadth of the Full AI Stack: None</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="n"/>
+      <c r="H109" s="1" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="D110" s="30" t="n">
+        <v>160</v>
+      </c>
+      <c r="E110" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F110" s="27" t="inlineStr">
+        <is>
+          <t>Americas Technology: Semiconductors: 3Q Preview: Expect stocks to work on better numbers following sector-wide pullback: None</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="n"/>
+      <c r="H110" s="1" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D111" s="30" t="n">
+        <v>130</v>
+      </c>
+      <c r="E111" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F111" s="27" t="inlineStr">
+        <is>
+          <t>Mobileye Global (MBLY.O): Initiating Coverage with a Buy Rating and a $11 PT</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="n"/>
+      <c r="H111" s="1" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D112" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="E112" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F112" s="27" t="inlineStr">
+        <is>
+          <t>Intel: Upgrading to Neutral – Approaching $85 PT; Although Turnaround Will Take Years, Mgmt Execution Has Been Solid, and Our Confidence Is Building; AI Will Continue to Be a Tailw</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="n"/>
+      <c r="H112" s="1" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr"/>
+      <c r="D113" s="30" t="n">
+        <v>110</v>
+      </c>
+      <c r="E113" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F113" s="27" t="inlineStr">
+        <is>
+          <t>Val. Trends #952: Rockets, Roadsters, and Air Taxis: Taking Transportation Vertical: Industry Overview</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="n"/>
+      <c r="H113" s="1" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr"/>
+      <c r="D114" s="30" t="n">
+        <v>105</v>
+      </c>
+      <c r="E114" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F114" s="27" t="inlineStr">
+        <is>
+          <t>Fundamentals Stronger Than Sentiment Heading Into3Q26 Earnings</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="n"/>
+      <c r="H114" s="1" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr"/>
+      <c r="D115" s="30" t="n">
+        <v>460</v>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F115" s="27" t="inlineStr">
+        <is>
+          <t>OEM/Supplier Preview: See some softness on OEM production challenges</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="n"/>
+      <c r="H115" s="1" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16165,9 +19601,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D2" s="37" t="inlineStr"/>
+      <c r="D2" s="41" t="inlineStr"/>
       <c r="E2" s="27" t="inlineStr"/>
-      <c r="F2" s="37" t="inlineStr"/>
+      <c r="F2" s="41" t="inlineStr"/>
       <c r="G2" s="27" t="n"/>
       <c r="H2" s="27" t="n"/>
       <c r="I2" s="27" t="n"/>
@@ -16186,9 +19622,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D3" s="38" t="inlineStr"/>
+      <c r="D3" s="42" t="inlineStr"/>
       <c r="E3" s="27" t="inlineStr"/>
-      <c r="F3" s="38" t="inlineStr"/>
+      <c r="F3" s="42" t="inlineStr"/>
       <c r="G3" s="27" t="n"/>
       <c r="H3" s="27" t="n"/>
       <c r="I3" s="27" t="n"/>
@@ -16207,9 +19643,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr"/>
+      <c r="D4" s="41" t="inlineStr"/>
       <c r="E4" s="27" t="inlineStr"/>
-      <c r="F4" s="37" t="inlineStr"/>
+      <c r="F4" s="41" t="inlineStr"/>
       <c r="G4" s="27" t="n"/>
       <c r="H4" s="27" t="n"/>
       <c r="I4" s="27" t="n"/>
@@ -16228,9 +19664,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr"/>
+      <c r="D5" s="42" t="inlineStr"/>
       <c r="E5" s="27" t="inlineStr"/>
-      <c r="F5" s="38" t="inlineStr"/>
+      <c r="F5" s="42" t="inlineStr"/>
       <c r="G5" s="27" t="n"/>
       <c r="H5" s="27" t="n"/>
       <c r="I5" s="27" t="n"/>
@@ -16249,17 +19685,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>10/20 收 7,712.57（+0.28%）：財報日分化——道指大漲逾 500 點（+1%）、S&amp;P 小漲、那指近平；GM 財報後跌約 7%、GE 跌 3.5%，3M 漲近 6% 領漲道指、NOC +4.5%。美伊斡旋消息令 WTI 原油回落 2.5% 至約 101 美元（此前八連漲累計逾 20%）。SPCX 與 NFLX 盤後財報前分別跌不足 1% 與近 2%。</t>
         </is>
       </c>
-      <c r="E6" s="39" t="inlineStr">
+      <c r="E6" s="43" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>X 上聚焦財報季分化與油價回落的通膨緩解含義；多方認為道指+500 點顯示資金輪動有序，空方提醒那指走弱、市場在 META/TSLA 週三財報前不敢追價。</t>
         </is>
@@ -16282,9 +19718,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr"/>
+      <c r="D7" s="42" t="inlineStr"/>
       <c r="E7" s="27" t="inlineStr"/>
-      <c r="F7" s="38" t="inlineStr"/>
+      <c r="F7" s="42" t="inlineStr"/>
       <c r="G7" s="27" t="n"/>
       <c r="H7" s="27" t="n"/>
       <c r="I7" s="27" t="n"/>
@@ -16303,17 +19739,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>10/20 漲 +4.84% 收 61.68：大型製藥股走強，Zacks 以 DCF 估算 BMY 價值 145 美元（遠高於現價）引發估值修復討論；8 月以來的 AstraZeneca 併購傳聞溢價仍在，Q3 財報 10/29 登場。YTD +19.4%、一年 +47.8%，明顯跑贏 S&amp;P。</t>
         </is>
       </c>
-      <c r="E8" s="39" t="inlineStr">
+      <c r="E8" s="43" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>X 上兩派拉鋸：價值派強調 DCF 大幅低估與併購期權價值；謹慎派引用 Wells Fargo 10/13 維持 Equal-Weight 且目標價 65→60 的下調，認為財報前追高风险不小。</t>
         </is>
@@ -16336,9 +19772,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr"/>
+      <c r="D9" s="42" t="inlineStr"/>
       <c r="E9" s="27" t="inlineStr"/>
-      <c r="F9" s="38" t="inlineStr"/>
+      <c r="F9" s="42" t="inlineStr"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
       <c r="I9" s="27" t="n"/>
@@ -16357,9 +19793,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D10" s="37" t="inlineStr"/>
+      <c r="D10" s="41" t="inlineStr"/>
       <c r="E10" s="27" t="inlineStr"/>
-      <c r="F10" s="37" t="inlineStr"/>
+      <c r="F10" s="41" t="inlineStr"/>
       <c r="G10" s="27" t="n"/>
       <c r="H10" s="27" t="n"/>
       <c r="I10" s="27" t="n"/>
@@ -16378,9 +19814,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr"/>
+      <c r="D11" s="42" t="inlineStr"/>
       <c r="E11" s="27" t="inlineStr"/>
-      <c r="F11" s="38" t="inlineStr"/>
+      <c r="F11" s="42" t="inlineStr"/>
       <c r="G11" s="27" t="n"/>
       <c r="H11" s="27" t="n"/>
       <c r="I11" s="27" t="n"/>
@@ -16399,9 +19835,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D12" s="37" t="inlineStr"/>
+      <c r="D12" s="41" t="inlineStr"/>
       <c r="E12" s="27" t="inlineStr"/>
-      <c r="F12" s="37" t="inlineStr"/>
+      <c r="F12" s="41" t="inlineStr"/>
       <c r="G12" s="27" t="n"/>
       <c r="H12" s="27" t="n"/>
       <c r="I12" s="27" t="n"/>
@@ -16420,17 +19856,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>10/20 漲 +3.95% 收 127.11，盤後續漲 1.5% 至 129：皮膚科生技 Veradermics 年初至今暴漲 285%，Cantor Fitzgerald 10/19 重申 Overweight；分析師平均目標價 164.83（高點 182）。下一次財報預估 11/12。</t>
         </is>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="44" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="F13" s="38" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>X 上小型生技玩家持續吹捧 MANE 為今年最強皮膚科標的，285% YTD 漲幅被反覆引用；少數聲音提醒臨床前階段估值已高、波動劇烈（日內區間 113.5-130.1）。</t>
         </is>
@@ -16453,17 +19889,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D14" s="37" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>10/20 漲 +3.44% 收 364.32：Morgan Stanley 維持 Overweight 但將目標價由 676 下調至 643（STX 則獲重申 Top Pick），另有一家投行新給予買入評級；Barron's 報導大摩力捧 STX/WDC 看 80% 上行空間。本月早些時候 Toshiba 競爭恐慌造成的跌幅被分析師視為買點。10/22（週四）盤後財報。</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="44" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="F14" s="37" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>X 上儲存股多頭聲量佔優：『AI 儲存超級週期』派引用 HAMR/UltraSMR 路線圖與 HDD 缺貨邏輯；空方則盯住 Toshiba 產能與財報前目標價下調，主流共識是等週四財報的定價數據再加倉。</t>
         </is>
@@ -16486,9 +19922,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr"/>
+      <c r="D15" s="42" t="inlineStr"/>
       <c r="E15" s="27" t="inlineStr"/>
-      <c r="F15" s="38" t="inlineStr"/>
+      <c r="F15" s="42" t="inlineStr"/>
       <c r="G15" s="27" t="n"/>
       <c r="H15" s="27" t="n"/>
       <c r="I15" s="27" t="n"/>
@@ -16507,9 +19943,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr"/>
+      <c r="D16" s="41" t="inlineStr"/>
       <c r="E16" s="27" t="inlineStr"/>
-      <c r="F16" s="37" t="inlineStr"/>
+      <c r="F16" s="41" t="inlineStr"/>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="27" t="n"/>
       <c r="I16" s="27" t="n"/>
@@ -16528,9 +19964,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr"/>
+      <c r="D17" s="42" t="inlineStr"/>
       <c r="E17" s="27" t="inlineStr"/>
-      <c r="F17" s="38" t="inlineStr"/>
+      <c r="F17" s="42" t="inlineStr"/>
       <c r="G17" s="27" t="n"/>
       <c r="H17" s="27" t="n"/>
       <c r="I17" s="27" t="n"/>
@@ -16549,17 +19985,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="41" t="inlineStr">
         <is>
           <t>10/20 大漲 +7.9% 收 196.55，為全榜最大漲幅：公司當日宣布 RASolve 308 三期試驗開始收案（zoldonrasib + pembrolizumab + 化療，一線 RAS G12D 非鱗狀 NSCLC）；此前 10/15 RASONQUE（daraxonrasib）獲 CHMP 正面意見建議歐盟批准用於轉移性胰臟癌，8 月已獲 FDA 批准為首個廣譜 RAS 標靶藥。多家賣方上調目標價。</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E18" s="44" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="F18" s="37" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>X 上腫瘤藥社群明顯轉多：RAS(ON) 平台從胰臟癌擴展至肺癌的三期佈局被視為管線深度證明；82% ORR（zoldonrasib+mFFX 一線 PDAC）數據持續被引用，討論焦點是 2027 年前後商業化放量節奏。</t>
         </is>
@@ -16582,9 +20018,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr"/>
+      <c r="D19" s="42" t="inlineStr"/>
       <c r="E19" s="27" t="inlineStr"/>
-      <c r="F19" s="38" t="inlineStr"/>
+      <c r="F19" s="42" t="inlineStr"/>
       <c r="G19" s="27" t="n"/>
       <c r="H19" s="27" t="n"/>
       <c r="I19" s="27" t="n"/>
@@ -16603,17 +20039,17 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D20" s="37" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>10/20 漲 +3.64% 收 153.24：生技族群全面走強——RVMD 三期啟動 +7.9%、BMY +4.8%、MANE +4.0%、ONC +3.9%，IBB 同步 +3.2% 收 210.5。FDA 年中以來對重症藥物審批的彈性態度持續支撐板塊情緒。</t>
         </is>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="E20" s="44" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="F20" s="37" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>X 上生技板塊情緒明顯回暖：『XBI 突破』與小型生技併購/臨床催化劑討論熱度上升，主流觀點認為監管紅利 + 降息預期組合對久期長的生技股最有利。</t>
         </is>
@@ -16636,9 +20072,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr"/>
+      <c r="D21" s="42" t="inlineStr"/>
       <c r="E21" s="27" t="inlineStr"/>
-      <c r="F21" s="38" t="inlineStr"/>
+      <c r="F21" s="42" t="inlineStr"/>
       <c r="G21" s="27" t="n"/>
       <c r="H21" s="27" t="n"/>
       <c r="I21" s="27" t="n"/>
@@ -16657,9 +20093,9 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D22" s="37" t="inlineStr"/>
+      <c r="D22" s="41" t="inlineStr"/>
       <c r="E22" s="27" t="inlineStr"/>
-      <c r="F22" s="37" t="inlineStr"/>
+      <c r="F22" s="41" t="inlineStr"/>
       <c r="G22" s="27" t="n"/>
       <c r="H22" s="27" t="n"/>
       <c r="I22" s="27" t="n"/>
@@ -16678,17 +20114,17 @@
           <t>TRANCHE 1/3</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>10/20 收 26,424.82（約 -0.02%）近乎持平：半導體族群走弱拖累（ARM -3.1%），市場在週三 META、TSLA、IBM 財報前轉趨謹慎；前一天晶片股強力反彈後出現獲利了結。</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr">
+      <c r="E23" s="43" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F23" s="38" t="inlineStr">
+      <c r="F23" s="42" t="inlineStr">
         <is>
           <t>X 討論集中在『AI 交易是否進入財報驗證期』：一派認為只是反彈後歇腳，一派指出高估值半導體開始被對沖（put 量增加），等待 Mag 7 資本開支指引定調。</t>
         </is>
@@ -16711,9 +20147,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr"/>
+      <c r="D24" s="41" t="inlineStr"/>
       <c r="E24" s="27" t="inlineStr"/>
-      <c r="F24" s="37" t="inlineStr"/>
+      <c r="F24" s="41" t="inlineStr"/>
       <c r="G24" s="27" t="n"/>
       <c r="H24" s="27" t="n"/>
       <c r="I24" s="27" t="n"/>
@@ -16732,9 +20168,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr"/>
+      <c r="D25" s="42" t="inlineStr"/>
       <c r="E25" s="27" t="inlineStr"/>
-      <c r="F25" s="38" t="inlineStr"/>
+      <c r="F25" s="42" t="inlineStr"/>
       <c r="G25" s="27" t="n"/>
       <c r="H25" s="27" t="n"/>
       <c r="I25" s="27" t="n"/>
@@ -16753,9 +20189,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr"/>
+      <c r="D26" s="41" t="inlineStr"/>
       <c r="E26" s="27" t="inlineStr"/>
-      <c r="F26" s="37" t="inlineStr"/>
+      <c r="F26" s="41" t="inlineStr"/>
       <c r="G26" s="27" t="n"/>
       <c r="H26" s="27" t="n"/>
       <c r="I26" s="27" t="n"/>
@@ -16774,17 +20210,17 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>10/20 跌 -1.59% 收 694.25，10/21（週三）盤後公布 Q3，電話會議 4:30pm ET：營收指引 610-640 億美元，共識約 632 億（年增約 23%）；EPS 共識分歧大（5.94-6.77），稅前利潤預計年減約 16%，主因 AI 基建重金投入——全年資本開支指引 1,300-1,450 億美元，Q2 自由現金流僅 7.84 億。</t>
         </is>
       </c>
-      <c r="E27" s="39" t="inlineStr">
+      <c r="E27" s="43" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F27" s="38" t="inlineStr">
+      <c r="F27" s="42" t="inlineStr">
         <is>
           <t>X 上核心爭議是『AI 資本開支何時見回報』：多方認為 23% 營收增長證明廣告引擎足以供養 capex；空方以 FCF 銳減與利潤下滑為由主張減倉，共識是財報重點不在數字而在 2027 年開支指引。</t>
         </is>
@@ -16807,9 +20243,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr"/>
+      <c r="D28" s="41" t="inlineStr"/>
       <c r="E28" s="27" t="inlineStr"/>
-      <c r="F28" s="37" t="inlineStr"/>
+      <c r="F28" s="41" t="inlineStr"/>
       <c r="G28" s="27" t="n"/>
       <c r="H28" s="27" t="n"/>
       <c r="I28" s="27" t="n"/>
@@ -16828,9 +20264,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr"/>
+      <c r="D29" s="42" t="inlineStr"/>
       <c r="E29" s="27" t="inlineStr"/>
-      <c r="F29" s="38" t="inlineStr"/>
+      <c r="F29" s="42" t="inlineStr"/>
       <c r="G29" s="27" t="n"/>
       <c r="H29" s="27" t="n"/>
       <c r="I29" s="27" t="n"/>
@@ -16849,9 +20285,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr"/>
+      <c r="D30" s="41" t="inlineStr"/>
       <c r="E30" s="27" t="inlineStr"/>
-      <c r="F30" s="37" t="inlineStr"/>
+      <c r="F30" s="41" t="inlineStr"/>
       <c r="G30" s="27" t="n"/>
       <c r="H30" s="27" t="n"/>
       <c r="I30" s="27" t="n"/>
@@ -16870,9 +20306,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr"/>
+      <c r="D31" s="42" t="inlineStr"/>
       <c r="E31" s="27" t="inlineStr"/>
-      <c r="F31" s="38" t="inlineStr"/>
+      <c r="F31" s="42" t="inlineStr"/>
       <c r="G31" s="27" t="n"/>
       <c r="H31" s="27" t="n"/>
       <c r="I31" s="27" t="n"/>
@@ -16891,9 +20327,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D32" s="37" t="inlineStr"/>
+      <c r="D32" s="41" t="inlineStr"/>
       <c r="E32" s="27" t="inlineStr"/>
-      <c r="F32" s="37" t="inlineStr"/>
+      <c r="F32" s="41" t="inlineStr"/>
       <c r="G32" s="27" t="n"/>
       <c r="H32" s="27" t="n"/>
       <c r="I32" s="27" t="n"/>
@@ -16912,9 +20348,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D33" s="38" t="inlineStr"/>
+      <c r="D33" s="42" t="inlineStr"/>
       <c r="E33" s="27" t="inlineStr"/>
-      <c r="F33" s="38" t="inlineStr"/>
+      <c r="F33" s="42" t="inlineStr"/>
       <c r="G33" s="27" t="n"/>
       <c r="H33" s="27" t="n"/>
       <c r="I33" s="27" t="n"/>
@@ -16933,9 +20369,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D34" s="37" t="inlineStr"/>
+      <c r="D34" s="41" t="inlineStr"/>
       <c r="E34" s="27" t="inlineStr"/>
-      <c r="F34" s="37" t="inlineStr"/>
+      <c r="F34" s="41" t="inlineStr"/>
       <c r="G34" s="27" t="n"/>
       <c r="H34" s="27" t="n"/>
       <c r="I34" s="27" t="n"/>
@@ -16954,9 +20390,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr"/>
+      <c r="D35" s="42" t="inlineStr"/>
       <c r="E35" s="27" t="inlineStr"/>
-      <c r="F35" s="38" t="inlineStr"/>
+      <c r="F35" s="42" t="inlineStr"/>
       <c r="G35" s="27" t="n"/>
       <c r="H35" s="27" t="n"/>
       <c r="I35" s="27" t="n"/>
@@ -16975,9 +20411,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D36" s="37" t="inlineStr"/>
+      <c r="D36" s="41" t="inlineStr"/>
       <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="37" t="inlineStr"/>
+      <c r="F36" s="41" t="inlineStr"/>
       <c r="G36" s="27" t="n"/>
       <c r="H36" s="27" t="n"/>
       <c r="I36" s="27" t="n"/>
@@ -16996,9 +20432,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr"/>
+      <c r="D37" s="42" t="inlineStr"/>
       <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="38" t="inlineStr"/>
+      <c r="F37" s="42" t="inlineStr"/>
       <c r="G37" s="27" t="n"/>
       <c r="H37" s="27" t="n"/>
       <c r="I37" s="27" t="n"/>
@@ -17017,9 +20453,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D38" s="37" t="inlineStr"/>
+      <c r="D38" s="41" t="inlineStr"/>
       <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="37" t="inlineStr"/>
+      <c r="F38" s="41" t="inlineStr"/>
       <c r="G38" s="27" t="n"/>
       <c r="H38" s="27" t="n"/>
       <c r="I38" s="27" t="n"/>
@@ -17038,9 +20474,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D39" s="38" t="inlineStr"/>
+      <c r="D39" s="42" t="inlineStr"/>
       <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="38" t="inlineStr"/>
+      <c r="F39" s="42" t="inlineStr"/>
       <c r="G39" s="27" t="n"/>
       <c r="H39" s="27" t="n"/>
       <c r="I39" s="27" t="n"/>
@@ -17059,9 +20495,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D40" s="37" t="inlineStr"/>
+      <c r="D40" s="41" t="inlineStr"/>
       <c r="E40" s="27" t="inlineStr"/>
-      <c r="F40" s="37" t="inlineStr"/>
+      <c r="F40" s="41" t="inlineStr"/>
       <c r="G40" s="27" t="n"/>
       <c r="H40" s="27" t="n"/>
       <c r="I40" s="27" t="n"/>
@@ -17080,9 +20516,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr"/>
+      <c r="D41" s="42" t="inlineStr"/>
       <c r="E41" s="27" t="inlineStr"/>
-      <c r="F41" s="38" t="inlineStr"/>
+      <c r="F41" s="42" t="inlineStr"/>
       <c r="G41" s="27" t="n"/>
       <c r="H41" s="27" t="n"/>
       <c r="I41" s="27" t="n"/>
@@ -17101,9 +20537,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D42" s="37" t="inlineStr"/>
+      <c r="D42" s="41" t="inlineStr"/>
       <c r="E42" s="27" t="inlineStr"/>
-      <c r="F42" s="37" t="inlineStr"/>
+      <c r="F42" s="41" t="inlineStr"/>
       <c r="G42" s="27" t="n"/>
       <c r="H42" s="27" t="n"/>
       <c r="I42" s="27" t="n"/>
@@ -17122,9 +20558,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D43" s="38" t="inlineStr"/>
+      <c r="D43" s="42" t="inlineStr"/>
       <c r="E43" s="27" t="inlineStr"/>
-      <c r="F43" s="38" t="inlineStr"/>
+      <c r="F43" s="42" t="inlineStr"/>
       <c r="G43" s="27" t="n"/>
       <c r="H43" s="27" t="n"/>
       <c r="I43" s="27" t="n"/>
@@ -17143,9 +20579,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D44" s="37" t="inlineStr"/>
+      <c r="D44" s="41" t="inlineStr"/>
       <c r="E44" s="27" t="inlineStr"/>
-      <c r="F44" s="37" t="inlineStr"/>
+      <c r="F44" s="41" t="inlineStr"/>
       <c r="G44" s="27" t="n"/>
       <c r="H44" s="27" t="n"/>
       <c r="I44" s="27" t="n"/>
@@ -17164,17 +20600,17 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D45" s="38" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>10/20 跌 -1.66% 收 68.69，盤後公布 Q3：EPS 0.87 美元優於預期 0.82，營收 128.7 億美元符合預期，惟夜盤續跌約 5.9% 至 64.6。今年累跌約 25%：上週宣布裁員 6%（約 1,000 人）並任命前 Disney 高管 Peter Rice 出任首席內容長；10 月有五家投行下調目標價，市場關注『注意力稀缺』與觀看時長流失至 YouTube。</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E45" s="45" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="F45" s="42" t="inlineStr">
         <is>
           <t>X 上偏空：『EPS beat 但股價照跌』被視為成長敘事失效的證據，裁員+換將被解讀為防守姿態；多頭僅剩估值派（較 4 月高點跌 35%），Sarandos『成長不如預期』的言論被大量轉引。</t>
         </is>
@@ -17197,9 +20633,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D46" s="37" t="inlineStr"/>
+      <c r="D46" s="41" t="inlineStr"/>
       <c r="E46" s="27" t="inlineStr"/>
-      <c r="F46" s="37" t="inlineStr"/>
+      <c r="F46" s="41" t="inlineStr"/>
       <c r="G46" s="27" t="n"/>
       <c r="H46" s="27" t="n"/>
       <c r="I46" s="27" t="n"/>
@@ -17218,9 +20654,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D47" s="38" t="inlineStr"/>
+      <c r="D47" s="42" t="inlineStr"/>
       <c r="E47" s="27" t="inlineStr"/>
-      <c r="F47" s="38" t="inlineStr"/>
+      <c r="F47" s="42" t="inlineStr"/>
       <c r="G47" s="27" t="n"/>
       <c r="H47" s="27" t="n"/>
       <c r="I47" s="27" t="n"/>
@@ -17239,9 +20675,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D48" s="37" t="inlineStr"/>
+      <c r="D48" s="41" t="inlineStr"/>
       <c r="E48" s="27" t="inlineStr"/>
-      <c r="F48" s="37" t="inlineStr"/>
+      <c r="F48" s="41" t="inlineStr"/>
       <c r="G48" s="27" t="n"/>
       <c r="H48" s="27" t="n"/>
       <c r="I48" s="27" t="n"/>
@@ -17260,9 +20696,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr"/>
+      <c r="D49" s="42" t="inlineStr"/>
       <c r="E49" s="27" t="inlineStr"/>
-      <c r="F49" s="38" t="inlineStr"/>
+      <c r="F49" s="42" t="inlineStr"/>
       <c r="G49" s="27" t="n"/>
       <c r="H49" s="27" t="n"/>
       <c r="I49" s="27" t="n"/>
@@ -17281,9 +20717,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D50" s="37" t="inlineStr"/>
+      <c r="D50" s="41" t="inlineStr"/>
       <c r="E50" s="27" t="inlineStr"/>
-      <c r="F50" s="37" t="inlineStr"/>
+      <c r="F50" s="41" t="inlineStr"/>
       <c r="G50" s="27" t="n"/>
       <c r="H50" s="27" t="n"/>
       <c r="I50" s="27" t="n"/>
@@ -17302,9 +20738,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D51" s="38" t="inlineStr"/>
+      <c r="D51" s="42" t="inlineStr"/>
       <c r="E51" s="27" t="inlineStr"/>
-      <c r="F51" s="38" t="inlineStr"/>
+      <c r="F51" s="42" t="inlineStr"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
       <c r="I51" s="27" t="n"/>
@@ -17323,9 +20759,9 @@
           <t>WATCHLIST</t>
         </is>
       </c>
-      <c r="D52" s="37" t="inlineStr"/>
+      <c r="D52" s="41" t="inlineStr"/>
       <c r="E52" s="27" t="inlineStr"/>
-      <c r="F52" s="37" t="inlineStr"/>
+      <c r="F52" s="41" t="inlineStr"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
       <c r="I52" s="27" t="n"/>
@@ -17344,9 +20780,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr"/>
+      <c r="D53" s="42" t="inlineStr"/>
       <c r="E53" s="27" t="inlineStr"/>
-      <c r="F53" s="38" t="inlineStr"/>
+      <c r="F53" s="42" t="inlineStr"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
       <c r="I53" s="27" t="n"/>
@@ -17365,9 +20801,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D54" s="37" t="inlineStr"/>
+      <c r="D54" s="41" t="inlineStr"/>
       <c r="E54" s="27" t="inlineStr"/>
-      <c r="F54" s="37" t="inlineStr"/>
+      <c r="F54" s="41" t="inlineStr"/>
       <c r="G54" s="27" t="n"/>
       <c r="H54" s="27" t="n"/>
       <c r="I54" s="27" t="n"/>
@@ -17386,9 +20822,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D55" s="38" t="inlineStr"/>
+      <c r="D55" s="42" t="inlineStr"/>
       <c r="E55" s="27" t="inlineStr"/>
-      <c r="F55" s="38" t="inlineStr"/>
+      <c r="F55" s="42" t="inlineStr"/>
       <c r="G55" s="27" t="n"/>
       <c r="H55" s="27" t="n"/>
       <c r="I55" s="27" t="n"/>
@@ -17407,9 +20843,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D56" s="37" t="inlineStr"/>
+      <c r="D56" s="41" t="inlineStr"/>
       <c r="E56" s="27" t="inlineStr"/>
-      <c r="F56" s="37" t="inlineStr"/>
+      <c r="F56" s="41" t="inlineStr"/>
       <c r="G56" s="27" t="n"/>
       <c r="H56" s="27" t="n"/>
       <c r="I56" s="27" t="n"/>
@@ -17428,9 +20864,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr"/>
+      <c r="D57" s="42" t="inlineStr"/>
       <c r="E57" s="27" t="inlineStr"/>
-      <c r="F57" s="38" t="inlineStr"/>
+      <c r="F57" s="42" t="inlineStr"/>
       <c r="G57" s="27" t="n"/>
       <c r="H57" s="27" t="n"/>
       <c r="I57" s="27" t="n"/>
@@ -17449,17 +20885,17 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D58" s="37" t="inlineStr">
+      <c r="D58" s="41" t="inlineStr">
         <is>
           <t>10/20 跌 -3.06% 收 221.06，為全榜最大跌幅：與 Qualcomm 的架構授權訴訟陪審團裁決餘波持續發酵，市場擔心長期權利金收入可預測性；半導體高估值族群獲利了結，財報前選擇權避險升溫（保護性 put 量增加、隱含波動率上升）。</t>
         </is>
       </c>
-      <c r="E58" s="41" t="inlineStr">
+      <c r="E58" s="45" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="F58" s="37" t="inlineStr">
+      <c r="F58" s="41" t="inlineStr">
         <is>
           <t>X 上偏空：訴訟不確定性 + 高本益比的組合被視為脆弱，『AI 資本支出放緩』的討論加深獲利了結壓力；多頭僅強調資料中心 CPU 滲透率的長線邏輯，短線普遍觀望財報。</t>
         </is>
@@ -17482,9 +20918,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D59" s="38" t="inlineStr"/>
+      <c r="D59" s="42" t="inlineStr"/>
       <c r="E59" s="27" t="inlineStr"/>
-      <c r="F59" s="38" t="inlineStr"/>
+      <c r="F59" s="42" t="inlineStr"/>
       <c r="G59" s="27" t="n"/>
       <c r="H59" s="27" t="n"/>
       <c r="I59" s="27" t="n"/>
@@ -17503,9 +20939,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D60" s="37" t="inlineStr"/>
+      <c r="D60" s="41" t="inlineStr"/>
       <c r="E60" s="27" t="inlineStr"/>
-      <c r="F60" s="37" t="inlineStr"/>
+      <c r="F60" s="41" t="inlineStr"/>
       <c r="G60" s="27" t="n"/>
       <c r="H60" s="27" t="n"/>
       <c r="I60" s="27" t="n"/>
@@ -17524,9 +20960,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D61" s="38" t="inlineStr"/>
+      <c r="D61" s="42" t="inlineStr"/>
       <c r="E61" s="27" t="inlineStr"/>
-      <c r="F61" s="38" t="inlineStr"/>
+      <c r="F61" s="42" t="inlineStr"/>
       <c r="G61" s="27" t="n"/>
       <c r="H61" s="27" t="n"/>
       <c r="I61" s="27" t="n"/>
@@ -17545,9 +20981,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D62" s="37" t="inlineStr"/>
+      <c r="D62" s="41" t="inlineStr"/>
       <c r="E62" s="27" t="inlineStr"/>
-      <c r="F62" s="37" t="inlineStr"/>
+      <c r="F62" s="41" t="inlineStr"/>
       <c r="G62" s="27" t="n"/>
       <c r="H62" s="27" t="n"/>
       <c r="I62" s="27" t="n"/>
@@ -17566,9 +21002,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D63" s="38" t="inlineStr"/>
+      <c r="D63" s="42" t="inlineStr"/>
       <c r="E63" s="27" t="inlineStr"/>
-      <c r="F63" s="38" t="inlineStr"/>
+      <c r="F63" s="42" t="inlineStr"/>
       <c r="G63" s="27" t="n"/>
       <c r="H63" s="27" t="n"/>
       <c r="I63" s="27" t="n"/>
@@ -17587,17 +21023,17 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D64" s="37" t="inlineStr">
+      <c r="D64" s="41" t="inlineStr">
         <is>
           <t>10/20 漲 +1.53% 收 373.71，10/21（週三）盤後公布 Q3：市場預期 EPS 約 0.44-0.45 美元（年減約 10-12%）、營收約 278-281 億美元（大致持平）；Q2 曾大幅 miss 34%，但本季交付量超出自家共識逾 2.4 萬輛。電話會議 5:30pm ET。</t>
         </is>
       </c>
-      <c r="E64" s="39" t="inlineStr">
+      <c r="E64" s="43" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F64" s="37" t="inlineStr">
+      <c r="F64" s="41" t="inlineStr">
         <is>
           <t>X 上照例兩極：多頭主打交付超預期與自動駕駛/能源敘事，空頭盯住利潤率連續收縮與 EPS 年減；多數交易員傾向財報後再定向，隱含波動率定價的單日波動不小。</t>
         </is>
@@ -17620,9 +21056,9 @@
           <t>AVOID/WAIT</t>
         </is>
       </c>
-      <c r="D65" s="38" t="inlineStr"/>
+      <c r="D65" s="42" t="inlineStr"/>
       <c r="E65" s="27" t="inlineStr"/>
-      <c r="F65" s="38" t="inlineStr"/>
+      <c r="F65" s="42" t="inlineStr"/>
       <c r="G65" s="27" t="n"/>
       <c r="H65" s="27" t="n"/>
       <c r="I65" s="27" t="n"/>
@@ -17639,7 +21075,7 @@
       <c r="I66" s="1" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="42" t="inlineStr">
+      <c r="A67" s="46" t="inlineStr">
         <is>
           <t>News: Yahoo Finance (top 3 headlines per ticker, linked). X opinion: agent web research on popular investor posts, focus list only (11 tickers), as of 2026-10-21. Sources: https://www.investopedia.com/stock-market-today-dow-jones-s-and-p-500-10202026-12183813; https://finance.yahoo.com/markets/stocks/articles/markets-news-oct-20-2026-103252254.html; https://www.investopedia.com/stock-market-today-dow-jones-s-and-p-500-10202026-12183813; https://www.tradingkey.com/news/market-movers/262226929-market-movers-arm-20261020; https://www.marketwatch.com/investing/stock/wdc; https://finance.yahoo.com/quote/WDC/; https://www.tipranks.com/news/seagate-and-western-digital-stocks-rebound-as-morgan-stanley-says-get-aggressive; https://ir.revmed.com/press-releases; https://www.tradingkey.com/news/market-movers/262226488-market-movers-rvmd-20261020; https://www.marketwatch.com/investing/stock/bmy; https://www.google.com/finance/quote/BMY:NYSE; https://finance.yahoo.com/quote/MANE/</t>
         </is>
@@ -17662,7 +21098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18066,3152 +21502,3152 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr"/>
-      <c r="C2" s="44" t="n">
+      <c r="B2" s="48" t="inlineStr"/>
+      <c r="C2" s="48" t="n">
         <v>71.28</v>
       </c>
-      <c r="D2" s="44" t="n">
+      <c r="D2" s="48" t="n">
         <v>78.45</v>
       </c>
-      <c r="E2" s="44" t="n">
+      <c r="E2" s="48" t="n">
         <v>78.42</v>
       </c>
-      <c r="F2" s="44" t="n">
+      <c r="F2" s="48" t="n">
         <v>77.97</v>
       </c>
-      <c r="G2" s="44" t="n">
+      <c r="G2" s="48" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="H2" s="44" t="inlineStr"/>
-      <c r="I2" s="44" t="inlineStr"/>
-      <c r="J2" s="44" t="n">
+      <c r="H2" s="48" t="inlineStr"/>
+      <c r="I2" s="48" t="inlineStr"/>
+      <c r="J2" s="48" t="n">
         <v>71.20999999999999</v>
       </c>
-      <c r="K2" s="44" t="n">
+      <c r="K2" s="48" t="n">
         <v>67.16</v>
       </c>
-      <c r="L2" s="44" t="n">
+      <c r="L2" s="48" t="n">
         <v>65.72</v>
       </c>
-      <c r="M2" s="44" t="inlineStr"/>
-      <c r="N2" s="44" t="n">
+      <c r="M2" s="48" t="inlineStr"/>
+      <c r="N2" s="48" t="n">
         <v>61.68</v>
       </c>
-      <c r="O2" s="44" t="n">
+      <c r="O2" s="48" t="n">
         <v>71.7</v>
       </c>
-      <c r="P2" s="44" t="n">
+      <c r="P2" s="48" t="n">
         <v>67.97</v>
       </c>
-      <c r="Q2" s="44" t="inlineStr"/>
-      <c r="R2" s="44" t="inlineStr"/>
-      <c r="S2" s="44" t="n">
+      <c r="Q2" s="48" t="inlineStr"/>
+      <c r="R2" s="48" t="inlineStr"/>
+      <c r="S2" s="48" t="n">
         <v>63.9</v>
       </c>
-      <c r="T2" s="44" t="inlineStr"/>
-      <c r="U2" s="44" t="n">
+      <c r="T2" s="48" t="inlineStr"/>
+      <c r="U2" s="48" t="n">
         <v>69.08</v>
       </c>
-      <c r="V2" s="44" t="inlineStr"/>
-      <c r="W2" s="44" t="n">
+      <c r="V2" s="48" t="inlineStr"/>
+      <c r="W2" s="48" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="X2" s="44" t="n">
+      <c r="X2" s="48" t="n">
         <v>78.70999999999999</v>
       </c>
-      <c r="Y2" s="44" t="inlineStr"/>
-      <c r="Z2" s="44" t="n">
+      <c r="Y2" s="48" t="inlineStr"/>
+      <c r="Z2" s="48" t="n">
         <v>59.47</v>
       </c>
-      <c r="AA2" s="44" t="n">
+      <c r="AA2" s="48" t="n">
         <v>63.46</v>
       </c>
-      <c r="AB2" s="44" t="n">
+      <c r="AB2" s="48" t="n">
         <v>50.97</v>
       </c>
-      <c r="AC2" s="44" t="inlineStr"/>
-      <c r="AD2" s="44" t="n">
+      <c r="AC2" s="48" t="inlineStr"/>
+      <c r="AD2" s="48" t="n">
         <v>49.4</v>
       </c>
-      <c r="AE2" s="44" t="n">
+      <c r="AE2" s="48" t="n">
         <v>48.12</v>
       </c>
-      <c r="AF2" s="44" t="n">
+      <c r="AF2" s="48" t="n">
         <v>64.16</v>
       </c>
-      <c r="AG2" s="44" t="inlineStr"/>
-      <c r="AH2" s="44" t="n">
+      <c r="AG2" s="48" t="inlineStr"/>
+      <c r="AH2" s="48" t="n">
         <v>53.49</v>
       </c>
-      <c r="AI2" s="44" t="inlineStr"/>
-      <c r="AJ2" s="44" t="inlineStr"/>
-      <c r="AK2" s="44" t="n">
+      <c r="AI2" s="48" t="inlineStr"/>
+      <c r="AJ2" s="48" t="inlineStr"/>
+      <c r="AK2" s="48" t="n">
         <v>52.13</v>
       </c>
-      <c r="AL2" s="44" t="n">
+      <c r="AL2" s="48" t="n">
         <v>49.6</v>
       </c>
-      <c r="AM2" s="44" t="n">
+      <c r="AM2" s="48" t="n">
         <v>69.7</v>
       </c>
-      <c r="AN2" s="44" t="n">
+      <c r="AN2" s="48" t="n">
         <v>46.21</v>
       </c>
-      <c r="AO2" s="44" t="inlineStr"/>
-      <c r="AP2" s="44" t="n">
+      <c r="AO2" s="48" t="inlineStr"/>
+      <c r="AP2" s="48" t="n">
         <v>50.65</v>
       </c>
-      <c r="AQ2" s="44" t="n">
+      <c r="AQ2" s="48" t="n">
         <v>34.76</v>
       </c>
-      <c r="AR2" s="44" t="n">
+      <c r="AR2" s="48" t="n">
         <v>61.87</v>
       </c>
-      <c r="AS2" s="44" t="n">
+      <c r="AS2" s="48" t="n">
         <v>45.76</v>
       </c>
-      <c r="AT2" s="44" t="n">
+      <c r="AT2" s="48" t="n">
         <v>42.32</v>
       </c>
-      <c r="AU2" s="44" t="n">
+      <c r="AU2" s="48" t="n">
         <v>43.39</v>
       </c>
-      <c r="AV2" s="44" t="n">
+      <c r="AV2" s="48" t="n">
         <v>51.57</v>
       </c>
-      <c r="AW2" s="44" t="inlineStr"/>
-      <c r="AX2" s="44" t="inlineStr"/>
-      <c r="AY2" s="44" t="n">
+      <c r="AW2" s="48" t="inlineStr"/>
+      <c r="AX2" s="48" t="inlineStr"/>
+      <c r="AY2" s="48" t="n">
         <v>48.27</v>
       </c>
-      <c r="AZ2" s="44" t="n">
+      <c r="AZ2" s="48" t="n">
         <v>54.14</v>
       </c>
-      <c r="BA2" s="44" t="n">
+      <c r="BA2" s="48" t="n">
         <v>36.25</v>
       </c>
-      <c r="BB2" s="44" t="n">
+      <c r="BB2" s="48" t="n">
         <v>26.83</v>
       </c>
-      <c r="BC2" s="44" t="inlineStr"/>
-      <c r="BD2" s="44" t="inlineStr"/>
-      <c r="BE2" s="44" t="n">
+      <c r="BC2" s="48" t="inlineStr"/>
+      <c r="BD2" s="48" t="inlineStr"/>
+      <c r="BE2" s="48" t="n">
         <v>31.48</v>
       </c>
-      <c r="BF2" s="44" t="n">
+      <c r="BF2" s="48" t="n">
         <v>40.44</v>
       </c>
-      <c r="BG2" s="44" t="n">
+      <c r="BG2" s="48" t="n">
         <v>42.04</v>
       </c>
-      <c r="BH2" s="44" t="inlineStr"/>
-      <c r="BI2" s="44" t="n">
+      <c r="BH2" s="48" t="inlineStr"/>
+      <c r="BI2" s="48" t="n">
         <v>46.91</v>
       </c>
-      <c r="BJ2" s="44" t="n">
+      <c r="BJ2" s="48" t="n">
         <v>22.54</v>
       </c>
-      <c r="BK2" s="44" t="inlineStr"/>
-      <c r="BL2" s="44" t="n">
+      <c r="BK2" s="48" t="inlineStr"/>
+      <c r="BL2" s="48" t="n">
         <v>24.14</v>
       </c>
-      <c r="BM2" s="44" t="n">
+      <c r="BM2" s="48" t="n">
         <v>31.07</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B3" s="44" t="inlineStr"/>
-      <c r="C3" s="44" t="n">
+      <c r="B3" s="48" t="inlineStr"/>
+      <c r="C3" s="48" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="D3" s="44" t="n">
+      <c r="D3" s="48" t="n">
         <v>76.04000000000001</v>
       </c>
-      <c r="E3" s="44" t="n">
+      <c r="E3" s="48" t="n">
         <v>75.53</v>
       </c>
-      <c r="F3" s="44" t="n">
+      <c r="F3" s="48" t="n">
         <v>74.97</v>
       </c>
-      <c r="G3" s="44" t="n">
+      <c r="G3" s="48" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="H3" s="44" t="inlineStr"/>
-      <c r="I3" s="44" t="inlineStr"/>
-      <c r="J3" s="44" t="n">
+      <c r="H3" s="48" t="inlineStr"/>
+      <c r="I3" s="48" t="inlineStr"/>
+      <c r="J3" s="48" t="n">
         <v>71.62</v>
       </c>
-      <c r="K3" s="44" t="n">
+      <c r="K3" s="48" t="n">
         <v>68.8</v>
       </c>
-      <c r="L3" s="44" t="n">
+      <c r="L3" s="48" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="M3" s="44" t="inlineStr"/>
-      <c r="N3" s="44" t="n">
+      <c r="M3" s="48" t="inlineStr"/>
+      <c r="N3" s="48" t="n">
         <v>64.73999999999999</v>
       </c>
-      <c r="O3" s="44" t="n">
+      <c r="O3" s="48" t="n">
         <v>69.55</v>
       </c>
-      <c r="P3" s="44" t="n">
+      <c r="P3" s="48" t="n">
         <v>69.05</v>
       </c>
-      <c r="Q3" s="44" t="inlineStr"/>
-      <c r="R3" s="44" t="inlineStr"/>
-      <c r="S3" s="44" t="n">
+      <c r="Q3" s="48" t="inlineStr"/>
+      <c r="R3" s="48" t="inlineStr"/>
+      <c r="S3" s="48" t="n">
         <v>66.73999999999999</v>
       </c>
-      <c r="T3" s="44" t="inlineStr"/>
-      <c r="U3" s="44" t="n">
+      <c r="T3" s="48" t="inlineStr"/>
+      <c r="U3" s="48" t="n">
         <v>67.23</v>
       </c>
-      <c r="V3" s="44" t="inlineStr"/>
-      <c r="W3" s="44" t="n">
+      <c r="V3" s="48" t="inlineStr"/>
+      <c r="W3" s="48" t="n">
         <v>70.69</v>
       </c>
-      <c r="X3" s="44" t="n">
+      <c r="X3" s="48" t="n">
         <v>79.19</v>
       </c>
-      <c r="Y3" s="44" t="inlineStr"/>
-      <c r="Z3" s="44" t="n">
+      <c r="Y3" s="48" t="inlineStr"/>
+      <c r="Z3" s="48" t="n">
         <v>60.19</v>
       </c>
-      <c r="AA3" s="44" t="n">
+      <c r="AA3" s="48" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="AB3" s="44" t="n">
+      <c r="AB3" s="48" t="n">
         <v>49.53</v>
       </c>
-      <c r="AC3" s="44" t="inlineStr"/>
-      <c r="AD3" s="44" t="n">
+      <c r="AC3" s="48" t="inlineStr"/>
+      <c r="AD3" s="48" t="n">
         <v>51.34</v>
       </c>
-      <c r="AE3" s="44" t="n">
+      <c r="AE3" s="48" t="n">
         <v>49.26</v>
       </c>
-      <c r="AF3" s="44" t="n">
+      <c r="AF3" s="48" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="AG3" s="44" t="inlineStr"/>
-      <c r="AH3" s="44" t="n">
+      <c r="AG3" s="48" t="inlineStr"/>
+      <c r="AH3" s="48" t="n">
         <v>55.54</v>
       </c>
-      <c r="AI3" s="44" t="inlineStr"/>
-      <c r="AJ3" s="44" t="inlineStr"/>
-      <c r="AK3" s="44" t="n">
+      <c r="AI3" s="48" t="inlineStr"/>
+      <c r="AJ3" s="48" t="inlineStr"/>
+      <c r="AK3" s="48" t="n">
         <v>54.28</v>
       </c>
-      <c r="AL3" s="44" t="n">
+      <c r="AL3" s="48" t="n">
         <v>49.14</v>
       </c>
-      <c r="AM3" s="44" t="n">
+      <c r="AM3" s="48" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="AN3" s="44" t="n">
+      <c r="AN3" s="48" t="n">
         <v>46.95</v>
       </c>
-      <c r="AO3" s="44" t="inlineStr"/>
-      <c r="AP3" s="44" t="n">
+      <c r="AO3" s="48" t="inlineStr"/>
+      <c r="AP3" s="48" t="n">
         <v>53.77</v>
       </c>
-      <c r="AQ3" s="44" t="n">
+      <c r="AQ3" s="48" t="n">
         <v>36.58</v>
       </c>
-      <c r="AR3" s="44" t="n">
+      <c r="AR3" s="48" t="n">
         <v>58.42</v>
       </c>
-      <c r="AS3" s="44" t="n">
+      <c r="AS3" s="48" t="n">
         <v>48.05</v>
       </c>
-      <c r="AT3" s="44" t="n">
+      <c r="AT3" s="48" t="n">
         <v>47.44</v>
       </c>
-      <c r="AU3" s="44" t="n">
+      <c r="AU3" s="48" t="n">
         <v>46.35</v>
       </c>
-      <c r="AV3" s="44" t="n">
+      <c r="AV3" s="48" t="n">
         <v>56.25</v>
       </c>
-      <c r="AW3" s="44" t="inlineStr"/>
-      <c r="AX3" s="44" t="inlineStr"/>
-      <c r="AY3" s="44" t="n">
+      <c r="AW3" s="48" t="inlineStr"/>
+      <c r="AX3" s="48" t="inlineStr"/>
+      <c r="AY3" s="48" t="n">
         <v>51.17</v>
       </c>
-      <c r="AZ3" s="44" t="n">
+      <c r="AZ3" s="48" t="n">
         <v>50.44</v>
       </c>
-      <c r="BA3" s="44" t="n">
+      <c r="BA3" s="48" t="n">
         <v>42.52</v>
       </c>
-      <c r="BB3" s="44" t="n">
+      <c r="BB3" s="48" t="n">
         <v>30.4</v>
       </c>
-      <c r="BC3" s="44" t="inlineStr"/>
-      <c r="BD3" s="44" t="inlineStr"/>
-      <c r="BE3" s="44" t="n">
+      <c r="BC3" s="48" t="inlineStr"/>
+      <c r="BD3" s="48" t="inlineStr"/>
+      <c r="BE3" s="48" t="n">
         <v>34.21</v>
       </c>
-      <c r="BF3" s="44" t="n">
+      <c r="BF3" s="48" t="n">
         <v>43.72</v>
       </c>
-      <c r="BG3" s="44" t="n">
+      <c r="BG3" s="48" t="n">
         <v>40.91</v>
       </c>
-      <c r="BH3" s="44" t="inlineStr"/>
-      <c r="BI3" s="44" t="n">
+      <c r="BH3" s="48" t="inlineStr"/>
+      <c r="BI3" s="48" t="n">
         <v>51.29</v>
       </c>
-      <c r="BJ3" s="44" t="n">
+      <c r="BJ3" s="48" t="n">
         <v>29.58</v>
       </c>
-      <c r="BK3" s="44" t="inlineStr"/>
-      <c r="BL3" s="44" t="n">
+      <c r="BK3" s="48" t="inlineStr"/>
+      <c r="BL3" s="48" t="n">
         <v>23.34</v>
       </c>
-      <c r="BM3" s="44" t="n">
+      <c r="BM3" s="48" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr"/>
-      <c r="C4" s="44" t="n">
+      <c r="B4" s="48" t="inlineStr"/>
+      <c r="C4" s="48" t="n">
         <v>71.0097</v>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="48" t="n">
         <v>75.1065</v>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="48" t="n">
         <v>74.6066</v>
       </c>
-      <c r="F4" s="44" t="n">
+      <c r="F4" s="48" t="n">
         <v>73.9876</v>
       </c>
-      <c r="G4" s="44" t="n">
+      <c r="G4" s="48" t="n">
         <v>78.1263</v>
       </c>
-      <c r="H4" s="44" t="inlineStr"/>
-      <c r="I4" s="44" t="inlineStr"/>
-      <c r="J4" s="44" t="n">
+      <c r="H4" s="48" t="inlineStr"/>
+      <c r="I4" s="48" t="inlineStr"/>
+      <c r="J4" s="48" t="n">
         <v>73.2824</v>
       </c>
-      <c r="K4" s="44" t="n">
+      <c r="K4" s="48" t="n">
         <v>69.6169</v>
       </c>
-      <c r="L4" s="44" t="n">
+      <c r="L4" s="48" t="n">
         <v>69.4161</v>
       </c>
-      <c r="M4" s="44" t="inlineStr"/>
-      <c r="N4" s="44" t="n">
+      <c r="M4" s="48" t="inlineStr"/>
+      <c r="N4" s="48" t="n">
         <v>64.8612</v>
       </c>
-      <c r="O4" s="44" t="n">
+      <c r="O4" s="48" t="n">
         <v>69.24209999999999</v>
       </c>
-      <c r="P4" s="44" t="n">
+      <c r="P4" s="48" t="n">
         <v>68.8892</v>
       </c>
-      <c r="Q4" s="44" t="inlineStr"/>
-      <c r="R4" s="44" t="inlineStr"/>
-      <c r="S4" s="44" t="n">
+      <c r="Q4" s="48" t="inlineStr"/>
+      <c r="R4" s="48" t="inlineStr"/>
+      <c r="S4" s="48" t="n">
         <v>64.158</v>
       </c>
-      <c r="T4" s="44" t="inlineStr"/>
-      <c r="U4" s="44" t="n">
+      <c r="T4" s="48" t="inlineStr"/>
+      <c r="U4" s="48" t="n">
         <v>67.0598</v>
       </c>
-      <c r="V4" s="44" t="inlineStr"/>
-      <c r="W4" s="44" t="n">
+      <c r="V4" s="48" t="inlineStr"/>
+      <c r="W4" s="48" t="n">
         <v>69.96299999999999</v>
       </c>
-      <c r="X4" s="44" t="n">
+      <c r="X4" s="48" t="n">
         <v>79.3313</v>
       </c>
-      <c r="Y4" s="44" t="inlineStr"/>
-      <c r="Z4" s="44" t="n">
+      <c r="Y4" s="48" t="inlineStr"/>
+      <c r="Z4" s="48" t="n">
         <v>60.2923</v>
       </c>
-      <c r="AA4" s="44" t="n">
+      <c r="AA4" s="48" t="n">
         <v>68.0067</v>
       </c>
-      <c r="AB4" s="44" t="n">
+      <c r="AB4" s="48" t="n">
         <v>49.1677</v>
       </c>
-      <c r="AC4" s="44" t="inlineStr"/>
-      <c r="AD4" s="44" t="n">
+      <c r="AC4" s="48" t="inlineStr"/>
+      <c r="AD4" s="48" t="n">
         <v>51.8253</v>
       </c>
-      <c r="AE4" s="44" t="n">
+      <c r="AE4" s="48" t="n">
         <v>48.6683</v>
       </c>
-      <c r="AF4" s="44" t="n">
+      <c r="AF4" s="48" t="n">
         <v>73.41419999999999</v>
       </c>
-      <c r="AG4" s="44" t="inlineStr"/>
-      <c r="AH4" s="44" t="n">
+      <c r="AG4" s="48" t="inlineStr"/>
+      <c r="AH4" s="48" t="n">
         <v>54.9977</v>
       </c>
-      <c r="AI4" s="44" t="inlineStr"/>
-      <c r="AJ4" s="44" t="inlineStr"/>
-      <c r="AK4" s="44" t="n">
+      <c r="AI4" s="48" t="inlineStr"/>
+      <c r="AJ4" s="48" t="inlineStr"/>
+      <c r="AK4" s="48" t="n">
         <v>54.9537</v>
       </c>
-      <c r="AL4" s="44" t="n">
+      <c r="AL4" s="48" t="n">
         <v>49.9371</v>
       </c>
-      <c r="AM4" s="44" t="n">
+      <c r="AM4" s="48" t="n">
         <v>65.3142</v>
       </c>
-      <c r="AN4" s="44" t="n">
+      <c r="AN4" s="48" t="n">
         <v>45.1982</v>
       </c>
-      <c r="AO4" s="44" t="inlineStr"/>
-      <c r="AP4" s="44" t="n">
+      <c r="AO4" s="48" t="inlineStr"/>
+      <c r="AP4" s="48" t="n">
         <v>53.6889</v>
       </c>
-      <c r="AQ4" s="44" t="n">
+      <c r="AQ4" s="48" t="n">
         <v>36.3856</v>
       </c>
-      <c r="AR4" s="44" t="n">
+      <c r="AR4" s="48" t="n">
         <v>59.6368</v>
       </c>
-      <c r="AS4" s="44" t="n">
+      <c r="AS4" s="48" t="n">
         <v>47.1478</v>
       </c>
-      <c r="AT4" s="44" t="n">
+      <c r="AT4" s="48" t="n">
         <v>45.6564</v>
       </c>
-      <c r="AU4" s="44" t="n">
+      <c r="AU4" s="48" t="n">
         <v>43.8351</v>
       </c>
-      <c r="AV4" s="44" t="n">
+      <c r="AV4" s="48" t="n">
         <v>57.7195</v>
       </c>
-      <c r="AW4" s="44" t="inlineStr"/>
-      <c r="AX4" s="44" t="inlineStr"/>
-      <c r="AY4" s="44" t="n">
+      <c r="AW4" s="48" t="inlineStr"/>
+      <c r="AX4" s="48" t="inlineStr"/>
+      <c r="AY4" s="48" t="n">
         <v>49.6364</v>
       </c>
-      <c r="AZ4" s="44" t="n">
+      <c r="AZ4" s="48" t="n">
         <v>50.9589</v>
       </c>
-      <c r="BA4" s="44" t="n">
+      <c r="BA4" s="48" t="n">
         <v>37.8363</v>
       </c>
-      <c r="BB4" s="44" t="n">
+      <c r="BB4" s="48" t="n">
         <v>29.3607</v>
       </c>
-      <c r="BC4" s="44" t="inlineStr"/>
-      <c r="BD4" s="44" t="inlineStr"/>
-      <c r="BE4" s="44" t="n">
+      <c r="BC4" s="48" t="inlineStr"/>
+      <c r="BD4" s="48" t="inlineStr"/>
+      <c r="BE4" s="48" t="n">
         <v>35.106</v>
       </c>
-      <c r="BF4" s="44" t="n">
+      <c r="BF4" s="48" t="n">
         <v>43.0833</v>
       </c>
-      <c r="BG4" s="44" t="n">
+      <c r="BG4" s="48" t="n">
         <v>41.5679</v>
       </c>
-      <c r="BH4" s="44" t="inlineStr"/>
-      <c r="BI4" s="44" t="n">
+      <c r="BH4" s="48" t="inlineStr"/>
+      <c r="BI4" s="48" t="n">
         <v>53.1985</v>
       </c>
-      <c r="BJ4" s="44" t="n">
+      <c r="BJ4" s="48" t="n">
         <v>29.3966</v>
       </c>
-      <c r="BK4" s="44" t="inlineStr"/>
-      <c r="BL4" s="44" t="n">
+      <c r="BK4" s="48" t="inlineStr"/>
+      <c r="BL4" s="48" t="n">
         <v>24.241</v>
       </c>
-      <c r="BM4" s="44" t="n">
+      <c r="BM4" s="48" t="n">
         <v>34.1068</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr"/>
-      <c r="C5" s="44" t="n">
+      <c r="B5" s="48" t="inlineStr"/>
+      <c r="C5" s="48" t="n">
         <v>70.22199999999999</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="48" t="n">
         <v>74.98269999999999</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="48" t="n">
         <v>74.4816</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="48" t="n">
         <v>73.9624</v>
       </c>
-      <c r="G5" s="44" t="n">
+      <c r="G5" s="48" t="n">
         <v>78.65479999999999</v>
       </c>
-      <c r="H5" s="44" t="inlineStr"/>
-      <c r="I5" s="44" t="inlineStr"/>
-      <c r="J5" s="44" t="n">
+      <c r="H5" s="48" t="inlineStr"/>
+      <c r="I5" s="48" t="inlineStr"/>
+      <c r="J5" s="48" t="n">
         <v>71.8635</v>
       </c>
-      <c r="K5" s="44" t="n">
+      <c r="K5" s="48" t="n">
         <v>68.74630000000001</v>
       </c>
-      <c r="L5" s="44" t="n">
+      <c r="L5" s="48" t="n">
         <v>70.1567</v>
       </c>
-      <c r="M5" s="44" t="inlineStr"/>
-      <c r="N5" s="44" t="n">
+      <c r="M5" s="48" t="inlineStr"/>
+      <c r="N5" s="48" t="n">
         <v>64.4761</v>
       </c>
-      <c r="O5" s="44" t="n">
+      <c r="O5" s="48" t="n">
         <v>69.13720000000001</v>
       </c>
-      <c r="P5" s="44" t="n">
+      <c r="P5" s="48" t="n">
         <v>68.3886</v>
       </c>
-      <c r="Q5" s="44" t="inlineStr"/>
-      <c r="R5" s="44" t="inlineStr"/>
-      <c r="S5" s="44" t="n">
+      <c r="Q5" s="48" t="inlineStr"/>
+      <c r="R5" s="48" t="inlineStr"/>
+      <c r="S5" s="48" t="n">
         <v>64.6677</v>
       </c>
-      <c r="T5" s="44" t="inlineStr"/>
-      <c r="U5" s="44" t="n">
+      <c r="T5" s="48" t="inlineStr"/>
+      <c r="U5" s="48" t="n">
         <v>66.7132</v>
       </c>
-      <c r="V5" s="44" t="inlineStr"/>
-      <c r="W5" s="44" t="n">
+      <c r="V5" s="48" t="inlineStr"/>
+      <c r="W5" s="48" t="n">
         <v>70.11060000000001</v>
       </c>
-      <c r="X5" s="44" t="n">
+      <c r="X5" s="48" t="n">
         <v>78.3186</v>
       </c>
-      <c r="Y5" s="44" t="inlineStr"/>
-      <c r="Z5" s="44" t="n">
+      <c r="Y5" s="48" t="inlineStr"/>
+      <c r="Z5" s="48" t="n">
         <v>60.514</v>
       </c>
-      <c r="AA5" s="44" t="n">
+      <c r="AA5" s="48" t="n">
         <v>68.78830000000001</v>
       </c>
-      <c r="AB5" s="44" t="n">
+      <c r="AB5" s="48" t="n">
         <v>50.8052</v>
       </c>
-      <c r="AC5" s="44" t="inlineStr"/>
-      <c r="AD5" s="44" t="n">
+      <c r="AC5" s="48" t="inlineStr"/>
+      <c r="AD5" s="48" t="n">
         <v>50.7272</v>
       </c>
-      <c r="AE5" s="44" t="n">
+      <c r="AE5" s="48" t="n">
         <v>46.536</v>
       </c>
-      <c r="AF5" s="44" t="n">
+      <c r="AF5" s="48" t="n">
         <v>73.71210000000001</v>
       </c>
-      <c r="AG5" s="44" t="inlineStr"/>
-      <c r="AH5" s="44" t="n">
+      <c r="AG5" s="48" t="inlineStr"/>
+      <c r="AH5" s="48" t="n">
         <v>54.5994</v>
       </c>
-      <c r="AI5" s="44" t="inlineStr"/>
-      <c r="AJ5" s="44" t="inlineStr"/>
-      <c r="AK5" s="44" t="n">
+      <c r="AI5" s="48" t="inlineStr"/>
+      <c r="AJ5" s="48" t="inlineStr"/>
+      <c r="AK5" s="48" t="n">
         <v>54.7951</v>
       </c>
-      <c r="AL5" s="44" t="n">
+      <c r="AL5" s="48" t="n">
         <v>49.7191</v>
       </c>
-      <c r="AM5" s="44" t="n">
+      <c r="AM5" s="48" t="n">
         <v>66.04179999999999</v>
       </c>
-      <c r="AN5" s="44" t="n">
+      <c r="AN5" s="48" t="n">
         <v>43.4571</v>
       </c>
-      <c r="AO5" s="44" t="inlineStr"/>
-      <c r="AP5" s="44" t="n">
+      <c r="AO5" s="48" t="inlineStr"/>
+      <c r="AP5" s="48" t="n">
         <v>53.7649</v>
       </c>
-      <c r="AQ5" s="44" t="n">
+      <c r="AQ5" s="48" t="n">
         <v>36.3768</v>
       </c>
-      <c r="AR5" s="44" t="n">
+      <c r="AR5" s="48" t="n">
         <v>59.8989</v>
       </c>
-      <c r="AS5" s="44" t="n">
+      <c r="AS5" s="48" t="n">
         <v>47.3814</v>
       </c>
-      <c r="AT5" s="44" t="n">
+      <c r="AT5" s="48" t="n">
         <v>45.4283</v>
       </c>
-      <c r="AU5" s="44" t="n">
+      <c r="AU5" s="48" t="n">
         <v>43.0282</v>
       </c>
-      <c r="AV5" s="44" t="n">
+      <c r="AV5" s="48" t="n">
         <v>56.7657</v>
       </c>
-      <c r="AW5" s="44" t="inlineStr"/>
-      <c r="AX5" s="44" t="inlineStr"/>
-      <c r="AY5" s="44" t="n">
+      <c r="AW5" s="48" t="inlineStr"/>
+      <c r="AX5" s="48" t="inlineStr"/>
+      <c r="AY5" s="48" t="n">
         <v>50.4989</v>
       </c>
-      <c r="AZ5" s="44" t="n">
+      <c r="AZ5" s="48" t="n">
         <v>50.8467</v>
       </c>
-      <c r="BA5" s="44" t="n">
+      <c r="BA5" s="48" t="n">
         <v>37.7559</v>
       </c>
-      <c r="BB5" s="44" t="n">
+      <c r="BB5" s="48" t="n">
         <v>29.5292</v>
       </c>
-      <c r="BC5" s="44" t="inlineStr"/>
-      <c r="BD5" s="44" t="inlineStr"/>
-      <c r="BE5" s="44" t="n">
+      <c r="BC5" s="48" t="inlineStr"/>
+      <c r="BD5" s="48" t="inlineStr"/>
+      <c r="BE5" s="48" t="n">
         <v>37.337</v>
       </c>
-      <c r="BF5" s="44" t="n">
+      <c r="BF5" s="48" t="n">
         <v>42.2105</v>
       </c>
-      <c r="BG5" s="44" t="n">
+      <c r="BG5" s="48" t="n">
         <v>41.0042</v>
       </c>
-      <c r="BH5" s="44" t="inlineStr"/>
-      <c r="BI5" s="44" t="n">
+      <c r="BH5" s="48" t="inlineStr"/>
+      <c r="BI5" s="48" t="n">
         <v>52.9805</v>
       </c>
-      <c r="BJ5" s="44" t="n">
+      <c r="BJ5" s="48" t="n">
         <v>30.2942</v>
       </c>
-      <c r="BK5" s="44" t="inlineStr"/>
-      <c r="BL5" s="44" t="n">
+      <c r="BK5" s="48" t="inlineStr"/>
+      <c r="BL5" s="48" t="n">
         <v>24.0617</v>
       </c>
-      <c r="BM5" s="44" t="n">
+      <c r="BM5" s="48" t="n">
         <v>31.5958</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr"/>
-      <c r="C6" s="44" t="n">
+      <c r="B6" s="48" t="inlineStr"/>
+      <c r="C6" s="48" t="n">
         <v>72.2004</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="48" t="n">
         <v>76.13290000000001</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="48" t="n">
         <v>75.69889999999999</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="48" t="n">
         <v>74.97450000000001</v>
       </c>
-      <c r="G6" s="44" t="n">
+      <c r="G6" s="48" t="n">
         <v>79.22</v>
       </c>
-      <c r="H6" s="44" t="inlineStr"/>
-      <c r="I6" s="44" t="inlineStr"/>
-      <c r="J6" s="44" t="n">
+      <c r="H6" s="48" t="inlineStr"/>
+      <c r="I6" s="48" t="inlineStr"/>
+      <c r="J6" s="48" t="n">
         <v>71.8974</v>
       </c>
-      <c r="K6" s="44" t="n">
+      <c r="K6" s="48" t="n">
         <v>68.759</v>
       </c>
-      <c r="L6" s="44" t="n">
+      <c r="L6" s="48" t="n">
         <v>71.0428</v>
       </c>
-      <c r="M6" s="44" t="inlineStr"/>
-      <c r="N6" s="44" t="n">
+      <c r="M6" s="48" t="inlineStr"/>
+      <c r="N6" s="48" t="n">
         <v>64.6091</v>
       </c>
-      <c r="O6" s="44" t="n">
+      <c r="O6" s="48" t="n">
         <v>69.89960000000001</v>
       </c>
-      <c r="P6" s="44" t="n">
+      <c r="P6" s="48" t="n">
         <v>69.2612</v>
       </c>
-      <c r="Q6" s="44" t="inlineStr"/>
-      <c r="R6" s="44" t="inlineStr"/>
-      <c r="S6" s="44" t="n">
+      <c r="Q6" s="48" t="inlineStr"/>
+      <c r="R6" s="48" t="inlineStr"/>
+      <c r="S6" s="48" t="n">
         <v>64.61499999999999</v>
       </c>
-      <c r="T6" s="44" t="inlineStr"/>
-      <c r="U6" s="44" t="n">
+      <c r="T6" s="48" t="inlineStr"/>
+      <c r="U6" s="48" t="n">
         <v>66.6345</v>
       </c>
-      <c r="V6" s="44" t="inlineStr"/>
-      <c r="W6" s="44" t="n">
+      <c r="V6" s="48" t="inlineStr"/>
+      <c r="W6" s="48" t="n">
         <v>69.46639999999999</v>
       </c>
-      <c r="X6" s="44" t="n">
+      <c r="X6" s="48" t="n">
         <v>80.1247</v>
       </c>
-      <c r="Y6" s="44" t="inlineStr"/>
-      <c r="Z6" s="44" t="n">
+      <c r="Y6" s="48" t="inlineStr"/>
+      <c r="Z6" s="48" t="n">
         <v>61.7957</v>
       </c>
-      <c r="AA6" s="44" t="n">
+      <c r="AA6" s="48" t="n">
         <v>68.657</v>
       </c>
-      <c r="AB6" s="44" t="n">
+      <c r="AB6" s="48" t="n">
         <v>51.4743</v>
       </c>
-      <c r="AC6" s="44" t="inlineStr"/>
-      <c r="AD6" s="44" t="n">
+      <c r="AC6" s="48" t="inlineStr"/>
+      <c r="AD6" s="48" t="n">
         <v>50.9731</v>
       </c>
-      <c r="AE6" s="44" t="n">
+      <c r="AE6" s="48" t="n">
         <v>46.4095</v>
       </c>
-      <c r="AF6" s="44" t="n">
+      <c r="AF6" s="48" t="n">
         <v>73.7141</v>
       </c>
-      <c r="AG6" s="44" t="inlineStr"/>
-      <c r="AH6" s="44" t="n">
+      <c r="AG6" s="48" t="inlineStr"/>
+      <c r="AH6" s="48" t="n">
         <v>55.464</v>
       </c>
-      <c r="AI6" s="44" t="inlineStr"/>
-      <c r="AJ6" s="44" t="inlineStr"/>
-      <c r="AK6" s="44" t="n">
+      <c r="AI6" s="48" t="inlineStr"/>
+      <c r="AJ6" s="48" t="inlineStr"/>
+      <c r="AK6" s="48" t="n">
         <v>55.0005</v>
       </c>
-      <c r="AL6" s="44" t="n">
+      <c r="AL6" s="48" t="n">
         <v>49.6885</v>
       </c>
-      <c r="AM6" s="44" t="n">
+      <c r="AM6" s="48" t="n">
         <v>66.33110000000001</v>
       </c>
-      <c r="AN6" s="44" t="n">
+      <c r="AN6" s="48" t="n">
         <v>43.5757</v>
       </c>
-      <c r="AO6" s="44" t="inlineStr"/>
-      <c r="AP6" s="44" t="n">
+      <c r="AO6" s="48" t="inlineStr"/>
+      <c r="AP6" s="48" t="n">
         <v>53.6868</v>
       </c>
-      <c r="AQ6" s="44" t="n">
+      <c r="AQ6" s="48" t="n">
         <v>36.4464</v>
       </c>
-      <c r="AR6" s="44" t="n">
+      <c r="AR6" s="48" t="n">
         <v>60.9934</v>
       </c>
-      <c r="AS6" s="44" t="n">
+      <c r="AS6" s="48" t="n">
         <v>46.8606</v>
       </c>
-      <c r="AT6" s="44" t="n">
+      <c r="AT6" s="48" t="n">
         <v>46.2548</v>
       </c>
-      <c r="AU6" s="44" t="n">
+      <c r="AU6" s="48" t="n">
         <v>44.3283</v>
       </c>
-      <c r="AV6" s="44" t="n">
+      <c r="AV6" s="48" t="n">
         <v>58.0937</v>
       </c>
-      <c r="AW6" s="44" t="inlineStr"/>
-      <c r="AX6" s="44" t="inlineStr"/>
-      <c r="AY6" s="44" t="n">
+      <c r="AW6" s="48" t="inlineStr"/>
+      <c r="AX6" s="48" t="inlineStr"/>
+      <c r="AY6" s="48" t="n">
         <v>50.2704</v>
       </c>
-      <c r="AZ6" s="44" t="n">
+      <c r="AZ6" s="48" t="n">
         <v>50.4472</v>
       </c>
-      <c r="BA6" s="44" t="n">
+      <c r="BA6" s="48" t="n">
         <v>38.8707</v>
       </c>
-      <c r="BB6" s="44" t="n">
+      <c r="BB6" s="48" t="n">
         <v>29.6855</v>
       </c>
-      <c r="BC6" s="44" t="inlineStr"/>
-      <c r="BD6" s="44" t="inlineStr"/>
-      <c r="BE6" s="44" t="n">
+      <c r="BC6" s="48" t="inlineStr"/>
+      <c r="BD6" s="48" t="inlineStr"/>
+      <c r="BE6" s="48" t="n">
         <v>38.5855</v>
       </c>
-      <c r="BF6" s="44" t="n">
+      <c r="BF6" s="48" t="n">
         <v>43.1558</v>
       </c>
-      <c r="BG6" s="44" t="n">
+      <c r="BG6" s="48" t="n">
         <v>41.133</v>
       </c>
-      <c r="BH6" s="44" t="inlineStr"/>
-      <c r="BI6" s="44" t="n">
+      <c r="BH6" s="48" t="inlineStr"/>
+      <c r="BI6" s="48" t="n">
         <v>53.2875</v>
       </c>
-      <c r="BJ6" s="44" t="n">
+      <c r="BJ6" s="48" t="n">
         <v>31.4811</v>
       </c>
-      <c r="BK6" s="44" t="inlineStr"/>
-      <c r="BL6" s="44" t="n">
+      <c r="BK6" s="48" t="inlineStr"/>
+      <c r="BL6" s="48" t="n">
         <v>23.3235</v>
       </c>
-      <c r="BM6" s="44" t="n">
+      <c r="BM6" s="48" t="n">
         <v>32.7852</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr"/>
-      <c r="C7" s="44" t="n">
+      <c r="B7" s="48" t="inlineStr"/>
+      <c r="C7" s="48" t="n">
         <v>70.8755</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="48" t="n">
         <v>70.8997</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="48" t="n">
         <v>69.7089</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="48" t="n">
         <v>72.3254</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="48" t="n">
         <v>77.0598</v>
       </c>
-      <c r="H7" s="44" t="inlineStr"/>
-      <c r="I7" s="44" t="inlineStr"/>
-      <c r="J7" s="44" t="n">
+      <c r="H7" s="48" t="inlineStr"/>
+      <c r="I7" s="48" t="inlineStr"/>
+      <c r="J7" s="48" t="n">
         <v>68.05710000000001</v>
       </c>
-      <c r="K7" s="44" t="n">
+      <c r="K7" s="48" t="n">
         <v>64.1271</v>
       </c>
-      <c r="L7" s="44" t="n">
+      <c r="L7" s="48" t="n">
         <v>66.3653</v>
       </c>
-      <c r="M7" s="44" t="inlineStr"/>
-      <c r="N7" s="44" t="n">
+      <c r="M7" s="48" t="inlineStr"/>
+      <c r="N7" s="48" t="n">
         <v>62.5511</v>
       </c>
-      <c r="O7" s="44" t="n">
+      <c r="O7" s="48" t="n">
         <v>70.7453</v>
       </c>
-      <c r="P7" s="44" t="n">
+      <c r="P7" s="48" t="n">
         <v>62.471</v>
       </c>
-      <c r="Q7" s="44" t="inlineStr"/>
-      <c r="R7" s="44" t="inlineStr"/>
-      <c r="S7" s="44" t="n">
+      <c r="Q7" s="48" t="inlineStr"/>
+      <c r="R7" s="48" t="inlineStr"/>
+      <c r="S7" s="48" t="n">
         <v>64.7876</v>
       </c>
-      <c r="T7" s="44" t="inlineStr"/>
-      <c r="U7" s="44" t="n">
+      <c r="T7" s="48" t="inlineStr"/>
+      <c r="U7" s="48" t="n">
         <v>65.55500000000001</v>
       </c>
-      <c r="V7" s="44" t="inlineStr"/>
-      <c r="W7" s="44" t="n">
+      <c r="V7" s="48" t="inlineStr"/>
+      <c r="W7" s="48" t="n">
         <v>68.9755</v>
       </c>
-      <c r="X7" s="44" t="n">
+      <c r="X7" s="48" t="n">
         <v>69.8644</v>
       </c>
-      <c r="Y7" s="44" t="inlineStr"/>
-      <c r="Z7" s="44" t="n">
+      <c r="Y7" s="48" t="inlineStr"/>
+      <c r="Z7" s="48" t="n">
         <v>60.667</v>
       </c>
-      <c r="AA7" s="44" t="n">
+      <c r="AA7" s="48" t="n">
         <v>67.35469999999999</v>
       </c>
-      <c r="AB7" s="44" t="n">
+      <c r="AB7" s="48" t="n">
         <v>54.8052</v>
       </c>
-      <c r="AC7" s="44" t="inlineStr"/>
-      <c r="AD7" s="44" t="n">
+      <c r="AC7" s="48" t="inlineStr"/>
+      <c r="AD7" s="48" t="n">
         <v>46.8968</v>
       </c>
-      <c r="AE7" s="44" t="n">
+      <c r="AE7" s="48" t="n">
         <v>45.1122</v>
       </c>
-      <c r="AF7" s="44" t="n">
+      <c r="AF7" s="48" t="n">
         <v>66.8835</v>
       </c>
-      <c r="AG7" s="44" t="inlineStr"/>
-      <c r="AH7" s="44" t="n">
+      <c r="AG7" s="48" t="inlineStr"/>
+      <c r="AH7" s="48" t="n">
         <v>54.867</v>
       </c>
-      <c r="AI7" s="44" t="inlineStr"/>
-      <c r="AJ7" s="44" t="inlineStr"/>
-      <c r="AK7" s="44" t="n">
+      <c r="AI7" s="48" t="inlineStr"/>
+      <c r="AJ7" s="48" t="inlineStr"/>
+      <c r="AK7" s="48" t="n">
         <v>52.4691</v>
       </c>
-      <c r="AL7" s="44" t="n">
+      <c r="AL7" s="48" t="n">
         <v>47.7972</v>
       </c>
-      <c r="AM7" s="44" t="n">
+      <c r="AM7" s="48" t="n">
         <v>61.5375</v>
       </c>
-      <c r="AN7" s="44" t="n">
+      <c r="AN7" s="48" t="n">
         <v>46.4777</v>
       </c>
-      <c r="AO7" s="44" t="inlineStr"/>
-      <c r="AP7" s="44" t="n">
+      <c r="AO7" s="48" t="inlineStr"/>
+      <c r="AP7" s="48" t="n">
         <v>54.3748</v>
       </c>
-      <c r="AQ7" s="44" t="n">
+      <c r="AQ7" s="48" t="n">
         <v>42.2644</v>
       </c>
-      <c r="AR7" s="44" t="n">
+      <c r="AR7" s="48" t="n">
         <v>60.7557</v>
       </c>
-      <c r="AS7" s="44" t="n">
+      <c r="AS7" s="48" t="n">
         <v>45.8298</v>
       </c>
-      <c r="AT7" s="44" t="n">
+      <c r="AT7" s="48" t="n">
         <v>45.5154</v>
       </c>
-      <c r="AU7" s="44" t="n">
+      <c r="AU7" s="48" t="n">
         <v>47.2356</v>
       </c>
-      <c r="AV7" s="44" t="n">
+      <c r="AV7" s="48" t="n">
         <v>52.8355</v>
       </c>
-      <c r="AW7" s="44" t="inlineStr"/>
-      <c r="AX7" s="44" t="inlineStr"/>
-      <c r="AY7" s="44" t="n">
+      <c r="AW7" s="48" t="inlineStr"/>
+      <c r="AX7" s="48" t="inlineStr"/>
+      <c r="AY7" s="48" t="n">
         <v>46.6373</v>
       </c>
-      <c r="AZ7" s="44" t="n">
+      <c r="AZ7" s="48" t="n">
         <v>50.5277</v>
       </c>
-      <c r="BA7" s="44" t="n">
+      <c r="BA7" s="48" t="n">
         <v>42.5143</v>
       </c>
-      <c r="BB7" s="44" t="n">
+      <c r="BB7" s="48" t="n">
         <v>29.7571</v>
       </c>
-      <c r="BC7" s="44" t="inlineStr"/>
-      <c r="BD7" s="44" t="inlineStr"/>
-      <c r="BE7" s="44" t="n">
+      <c r="BC7" s="48" t="inlineStr"/>
+      <c r="BD7" s="48" t="inlineStr"/>
+      <c r="BE7" s="48" t="n">
         <v>45.5625</v>
       </c>
-      <c r="BF7" s="44" t="n">
+      <c r="BF7" s="48" t="n">
         <v>36.1222</v>
       </c>
-      <c r="BG7" s="44" t="n">
+      <c r="BG7" s="48" t="n">
         <v>42.4858</v>
       </c>
-      <c r="BH7" s="44" t="inlineStr"/>
-      <c r="BI7" s="44" t="n">
+      <c r="BH7" s="48" t="inlineStr"/>
+      <c r="BI7" s="48" t="n">
         <v>46.1188</v>
       </c>
-      <c r="BJ7" s="44" t="n">
+      <c r="BJ7" s="48" t="n">
         <v>37.6985</v>
       </c>
-      <c r="BK7" s="44" t="inlineStr"/>
-      <c r="BL7" s="44" t="n">
+      <c r="BK7" s="48" t="inlineStr"/>
+      <c r="BL7" s="48" t="n">
         <v>23.6546</v>
       </c>
-      <c r="BM7" s="44" t="n">
+      <c r="BM7" s="48" t="n">
         <v>33.4391</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr"/>
-      <c r="C8" s="44" t="n">
+      <c r="B8" s="48" t="inlineStr"/>
+      <c r="C8" s="48" t="n">
         <v>71.06140000000001</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="48" t="n">
         <v>70.2004</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="48" t="n">
         <v>69.19880000000001</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="48" t="n">
         <v>71.9072</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="48" t="n">
         <v>76.6712</v>
       </c>
-      <c r="H8" s="44" t="inlineStr"/>
-      <c r="I8" s="44" t="inlineStr"/>
-      <c r="J8" s="44" t="n">
+      <c r="H8" s="48" t="inlineStr"/>
+      <c r="I8" s="48" t="inlineStr"/>
+      <c r="J8" s="48" t="n">
         <v>67.9687</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="48" t="n">
         <v>63.4854</v>
       </c>
-      <c r="L8" s="44" t="n">
+      <c r="L8" s="48" t="n">
         <v>66.4628</v>
       </c>
-      <c r="M8" s="44" t="inlineStr"/>
-      <c r="N8" s="44" t="n">
+      <c r="M8" s="48" t="inlineStr"/>
+      <c r="N8" s="48" t="n">
         <v>62.3072</v>
       </c>
-      <c r="O8" s="44" t="n">
+      <c r="O8" s="48" t="n">
         <v>70.0104</v>
       </c>
-      <c r="P8" s="44" t="n">
+      <c r="P8" s="48" t="n">
         <v>61.9254</v>
       </c>
-      <c r="Q8" s="44" t="inlineStr"/>
-      <c r="R8" s="44" t="inlineStr"/>
-      <c r="S8" s="44" t="n">
+      <c r="Q8" s="48" t="inlineStr"/>
+      <c r="R8" s="48" t="inlineStr"/>
+      <c r="S8" s="48" t="n">
         <v>65.2561</v>
       </c>
-      <c r="T8" s="44" t="inlineStr"/>
-      <c r="U8" s="44" t="n">
+      <c r="T8" s="48" t="inlineStr"/>
+      <c r="U8" s="48" t="n">
         <v>65.1452</v>
       </c>
-      <c r="V8" s="44" t="inlineStr"/>
-      <c r="W8" s="44" t="n">
+      <c r="V8" s="48" t="inlineStr"/>
+      <c r="W8" s="48" t="n">
         <v>68.47969999999999</v>
       </c>
-      <c r="X8" s="44" t="n">
+      <c r="X8" s="48" t="n">
         <v>70.56659999999999</v>
       </c>
-      <c r="Y8" s="44" t="inlineStr"/>
-      <c r="Z8" s="44" t="n">
+      <c r="Y8" s="48" t="inlineStr"/>
+      <c r="Z8" s="48" t="n">
         <v>60.6969</v>
       </c>
-      <c r="AA8" s="44" t="n">
+      <c r="AA8" s="48" t="n">
         <v>67.43729999999999</v>
       </c>
-      <c r="AB8" s="44" t="n">
+      <c r="AB8" s="48" t="n">
         <v>55.1234</v>
       </c>
-      <c r="AC8" s="44" t="inlineStr"/>
-      <c r="AD8" s="44" t="n">
+      <c r="AC8" s="48" t="inlineStr"/>
+      <c r="AD8" s="48" t="n">
         <v>48.1937</v>
       </c>
-      <c r="AE8" s="44" t="n">
+      <c r="AE8" s="48" t="n">
         <v>45.2702</v>
       </c>
-      <c r="AF8" s="44" t="n">
+      <c r="AF8" s="48" t="n">
         <v>66.03270000000001</v>
       </c>
-      <c r="AG8" s="44" t="inlineStr"/>
-      <c r="AH8" s="44" t="n">
+      <c r="AG8" s="48" t="inlineStr"/>
+      <c r="AH8" s="48" t="n">
         <v>55.559</v>
       </c>
-      <c r="AI8" s="44" t="inlineStr"/>
-      <c r="AJ8" s="44" t="inlineStr"/>
-      <c r="AK8" s="44" t="n">
+      <c r="AI8" s="48" t="inlineStr"/>
+      <c r="AJ8" s="48" t="inlineStr"/>
+      <c r="AK8" s="48" t="n">
         <v>52.7709</v>
       </c>
-      <c r="AL8" s="44" t="n">
+      <c r="AL8" s="48" t="n">
         <v>47.5369</v>
       </c>
-      <c r="AM8" s="44" t="n">
+      <c r="AM8" s="48" t="n">
         <v>59.5939</v>
       </c>
-      <c r="AN8" s="44" t="n">
+      <c r="AN8" s="48" t="n">
         <v>47.1647</v>
       </c>
-      <c r="AO8" s="44" t="inlineStr"/>
-      <c r="AP8" s="44" t="n">
+      <c r="AO8" s="48" t="inlineStr"/>
+      <c r="AP8" s="48" t="n">
         <v>54.1551</v>
       </c>
-      <c r="AQ8" s="44" t="n">
+      <c r="AQ8" s="48" t="n">
         <v>42.3437</v>
       </c>
-      <c r="AR8" s="44" t="n">
+      <c r="AR8" s="48" t="n">
         <v>60.6358</v>
       </c>
-      <c r="AS8" s="44" t="n">
+      <c r="AS8" s="48" t="n">
         <v>47.1006</v>
       </c>
-      <c r="AT8" s="44" t="n">
+      <c r="AT8" s="48" t="n">
         <v>46.1808</v>
       </c>
-      <c r="AU8" s="44" t="n">
+      <c r="AU8" s="48" t="n">
         <v>48.035</v>
       </c>
-      <c r="AV8" s="44" t="n">
+      <c r="AV8" s="48" t="n">
         <v>52.4753</v>
       </c>
-      <c r="AW8" s="44" t="inlineStr"/>
-      <c r="AX8" s="44" t="inlineStr"/>
-      <c r="AY8" s="44" t="n">
+      <c r="AW8" s="48" t="inlineStr"/>
+      <c r="AX8" s="48" t="inlineStr"/>
+      <c r="AY8" s="48" t="n">
         <v>47.3826</v>
       </c>
-      <c r="AZ8" s="44" t="n">
+      <c r="AZ8" s="48" t="n">
         <v>49.4098</v>
       </c>
-      <c r="BA8" s="44" t="n">
+      <c r="BA8" s="48" t="n">
         <v>43.9237</v>
       </c>
-      <c r="BB8" s="44" t="n">
+      <c r="BB8" s="48" t="n">
         <v>30.4505</v>
       </c>
-      <c r="BC8" s="44" t="inlineStr"/>
-      <c r="BD8" s="44" t="inlineStr"/>
-      <c r="BE8" s="44" t="n">
+      <c r="BC8" s="48" t="inlineStr"/>
+      <c r="BD8" s="48" t="inlineStr"/>
+      <c r="BE8" s="48" t="n">
         <v>45.2983</v>
       </c>
-      <c r="BF8" s="44" t="n">
+      <c r="BF8" s="48" t="n">
         <v>36.8753</v>
       </c>
-      <c r="BG8" s="44" t="n">
+      <c r="BG8" s="48" t="n">
         <v>42.6475</v>
       </c>
-      <c r="BH8" s="44" t="inlineStr"/>
-      <c r="BI8" s="44" t="n">
+      <c r="BH8" s="48" t="inlineStr"/>
+      <c r="BI8" s="48" t="n">
         <v>44.857</v>
       </c>
-      <c r="BJ8" s="44" t="n">
+      <c r="BJ8" s="48" t="n">
         <v>36.8616</v>
       </c>
-      <c r="BK8" s="44" t="inlineStr"/>
-      <c r="BL8" s="44" t="n">
+      <c r="BK8" s="48" t="inlineStr"/>
+      <c r="BL8" s="48" t="n">
         <v>21.8137</v>
       </c>
-      <c r="BM8" s="44" t="n">
+      <c r="BM8" s="48" t="n">
         <v>34.1327</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr"/>
-      <c r="C9" s="44" t="n">
+      <c r="B9" s="48" t="inlineStr"/>
+      <c r="C9" s="48" t="n">
         <v>70.7697</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="48" t="n">
         <v>69.4632</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="48" t="n">
         <v>69.3738</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="48" t="n">
         <v>71.3081</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="48" t="n">
         <v>77.7761</v>
       </c>
-      <c r="H9" s="44" t="inlineStr"/>
-      <c r="I9" s="44" t="inlineStr"/>
-      <c r="J9" s="44" t="n">
+      <c r="H9" s="48" t="inlineStr"/>
+      <c r="I9" s="48" t="inlineStr"/>
+      <c r="J9" s="48" t="n">
         <v>73.712</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="48" t="n">
         <v>67.01860000000001</v>
       </c>
-      <c r="L9" s="44" t="n">
+      <c r="L9" s="48" t="n">
         <v>68.1799</v>
       </c>
-      <c r="M9" s="44" t="inlineStr"/>
-      <c r="N9" s="44" t="n">
+      <c r="M9" s="48" t="inlineStr"/>
+      <c r="N9" s="48" t="n">
         <v>62.9683</v>
       </c>
-      <c r="O9" s="44" t="n">
+      <c r="O9" s="48" t="n">
         <v>70.4499</v>
       </c>
-      <c r="P9" s="44" t="n">
+      <c r="P9" s="48" t="n">
         <v>64.63039999999999</v>
       </c>
-      <c r="Q9" s="44" t="inlineStr"/>
-      <c r="R9" s="44" t="inlineStr"/>
-      <c r="S9" s="44" t="n">
+      <c r="Q9" s="48" t="inlineStr"/>
+      <c r="R9" s="48" t="inlineStr"/>
+      <c r="S9" s="48" t="n">
         <v>64.9674</v>
       </c>
-      <c r="T9" s="44" t="inlineStr"/>
-      <c r="U9" s="44" t="n">
+      <c r="T9" s="48" t="inlineStr"/>
+      <c r="U9" s="48" t="n">
         <v>63.7939</v>
       </c>
-      <c r="V9" s="44" t="inlineStr"/>
-      <c r="W9" s="44" t="n">
+      <c r="V9" s="48" t="inlineStr"/>
+      <c r="W9" s="48" t="n">
         <v>68.1939</v>
       </c>
-      <c r="X9" s="44" t="n">
+      <c r="X9" s="48" t="n">
         <v>73.82850000000001</v>
       </c>
-      <c r="Y9" s="44" t="n">
+      <c r="Y9" s="48" t="n">
         <v>59.8734</v>
       </c>
-      <c r="Z9" s="44" t="n">
+      <c r="Z9" s="48" t="n">
         <v>62.6723</v>
       </c>
-      <c r="AA9" s="44" t="n">
+      <c r="AA9" s="48" t="n">
         <v>65.7046</v>
       </c>
-      <c r="AB9" s="44" t="n">
+      <c r="AB9" s="48" t="n">
         <v>51.6606</v>
       </c>
-      <c r="AC9" s="44" t="n">
+      <c r="AC9" s="48" t="n">
         <v>56.6381</v>
       </c>
-      <c r="AD9" s="44" t="n">
+      <c r="AD9" s="48" t="n">
         <v>51.488</v>
       </c>
-      <c r="AE9" s="44" t="n">
+      <c r="AE9" s="48" t="n">
         <v>48.3879</v>
       </c>
-      <c r="AF9" s="44" t="n">
+      <c r="AF9" s="48" t="n">
         <v>71.075</v>
       </c>
-      <c r="AG9" s="44" t="n">
+      <c r="AG9" s="48" t="n">
         <v>52.2603</v>
       </c>
-      <c r="AH9" s="44" t="n">
+      <c r="AH9" s="48" t="n">
         <v>54.6593</v>
       </c>
-      <c r="AI9" s="44" t="inlineStr"/>
-      <c r="AJ9" s="44" t="n">
+      <c r="AI9" s="48" t="inlineStr"/>
+      <c r="AJ9" s="48" t="n">
         <v>49.4682</v>
       </c>
-      <c r="AK9" s="44" t="n">
+      <c r="AK9" s="48" t="n">
         <v>52.2997</v>
       </c>
-      <c r="AL9" s="44" t="n">
+      <c r="AL9" s="48" t="n">
         <v>49.7907</v>
       </c>
-      <c r="AM9" s="44" t="n">
+      <c r="AM9" s="48" t="n">
         <v>58.7988</v>
       </c>
-      <c r="AN9" s="44" t="n">
+      <c r="AN9" s="48" t="n">
         <v>45.7971</v>
       </c>
-      <c r="AO9" s="44" t="inlineStr"/>
-      <c r="AP9" s="44" t="n">
+      <c r="AO9" s="48" t="inlineStr"/>
+      <c r="AP9" s="48" t="n">
         <v>51.5663</v>
       </c>
-      <c r="AQ9" s="44" t="n">
+      <c r="AQ9" s="48" t="n">
         <v>42.9515</v>
       </c>
-      <c r="AR9" s="44" t="n">
+      <c r="AR9" s="48" t="n">
         <v>60.079</v>
       </c>
-      <c r="AS9" s="44" t="n">
+      <c r="AS9" s="48" t="n">
         <v>47.5835</v>
       </c>
-      <c r="AT9" s="44" t="n">
+      <c r="AT9" s="48" t="n">
         <v>47.7537</v>
       </c>
-      <c r="AU9" s="44" t="n">
+      <c r="AU9" s="48" t="n">
         <v>49.7266</v>
       </c>
-      <c r="AV9" s="44" t="n">
+      <c r="AV9" s="48" t="n">
         <v>54.0579</v>
       </c>
-      <c r="AW9" s="44" t="n">
+      <c r="AW9" s="48" t="n">
         <v>48.0176</v>
       </c>
-      <c r="AX9" s="44" t="inlineStr"/>
-      <c r="AY9" s="44" t="n">
+      <c r="AX9" s="48" t="inlineStr"/>
+      <c r="AY9" s="48" t="n">
         <v>49.3894</v>
       </c>
-      <c r="AZ9" s="44" t="n">
+      <c r="AZ9" s="48" t="n">
         <v>50.1312</v>
       </c>
-      <c r="BA9" s="44" t="n">
+      <c r="BA9" s="48" t="n">
         <v>46.1365</v>
       </c>
-      <c r="BB9" s="44" t="n">
+      <c r="BB9" s="48" t="n">
         <v>31.4366</v>
       </c>
-      <c r="BC9" s="44" t="inlineStr"/>
-      <c r="BD9" s="44" t="n">
+      <c r="BC9" s="48" t="inlineStr"/>
+      <c r="BD9" s="48" t="n">
         <v>47.365</v>
       </c>
-      <c r="BE9" s="44" t="n">
+      <c r="BE9" s="48" t="n">
         <v>45.8193</v>
       </c>
-      <c r="BF9" s="44" t="n">
+      <c r="BF9" s="48" t="n">
         <v>37.8889</v>
       </c>
-      <c r="BG9" s="44" t="n">
+      <c r="BG9" s="48" t="n">
         <v>41.3463</v>
       </c>
-      <c r="BH9" s="44" t="inlineStr"/>
-      <c r="BI9" s="44" t="n">
+      <c r="BH9" s="48" t="inlineStr"/>
+      <c r="BI9" s="48" t="n">
         <v>47.1661</v>
       </c>
-      <c r="BJ9" s="44" t="n">
+      <c r="BJ9" s="48" t="n">
         <v>34.7735</v>
       </c>
-      <c r="BK9" s="44" t="inlineStr"/>
-      <c r="BL9" s="44" t="n">
+      <c r="BK9" s="48" t="inlineStr"/>
+      <c r="BL9" s="48" t="n">
         <v>23.9152</v>
       </c>
-      <c r="BM9" s="44" t="n">
+      <c r="BM9" s="48" t="n">
         <v>41.7517</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr"/>
-      <c r="C10" s="44" t="n">
+      <c r="B10" s="48" t="inlineStr"/>
+      <c r="C10" s="48" t="n">
         <v>71.5718</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="48" t="n">
         <v>70.35599999999999</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="48" t="n">
         <v>71.7107</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="48" t="n">
         <v>73.7787</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="48" t="n">
         <v>78.3218</v>
       </c>
-      <c r="H10" s="44" t="inlineStr"/>
-      <c r="I10" s="44" t="inlineStr"/>
-      <c r="J10" s="44" t="n">
+      <c r="H10" s="48" t="inlineStr"/>
+      <c r="I10" s="48" t="inlineStr"/>
+      <c r="J10" s="48" t="n">
         <v>74.2222</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="48" t="n">
         <v>63.7341</v>
       </c>
-      <c r="L10" s="44" t="n">
+      <c r="L10" s="48" t="n">
         <v>66.54130000000001</v>
       </c>
-      <c r="M10" s="44" t="inlineStr"/>
-      <c r="N10" s="44" t="n">
+      <c r="M10" s="48" t="inlineStr"/>
+      <c r="N10" s="48" t="n">
         <v>57.5673</v>
       </c>
-      <c r="O10" s="44" t="n">
+      <c r="O10" s="48" t="n">
         <v>70.9893</v>
       </c>
-      <c r="P10" s="44" t="n">
+      <c r="P10" s="48" t="n">
         <v>66.6961</v>
       </c>
-      <c r="Q10" s="44" t="inlineStr"/>
-      <c r="R10" s="44" t="inlineStr"/>
-      <c r="S10" s="44" t="n">
+      <c r="Q10" s="48" t="inlineStr"/>
+      <c r="R10" s="48" t="inlineStr"/>
+      <c r="S10" s="48" t="n">
         <v>66.7704</v>
       </c>
-      <c r="T10" s="44" t="inlineStr"/>
-      <c r="U10" s="44" t="n">
+      <c r="T10" s="48" t="inlineStr"/>
+      <c r="U10" s="48" t="n">
         <v>65.28189999999999</v>
       </c>
-      <c r="V10" s="44" t="inlineStr"/>
-      <c r="W10" s="44" t="n">
+      <c r="V10" s="48" t="inlineStr"/>
+      <c r="W10" s="48" t="n">
         <v>70.4559</v>
       </c>
-      <c r="X10" s="44" t="n">
+      <c r="X10" s="48" t="n">
         <v>73.2196</v>
       </c>
-      <c r="Y10" s="44" t="n">
+      <c r="Y10" s="48" t="n">
         <v>60.8367</v>
       </c>
-      <c r="Z10" s="44" t="n">
+      <c r="Z10" s="48" t="n">
         <v>57.9497</v>
       </c>
-      <c r="AA10" s="44" t="n">
+      <c r="AA10" s="48" t="n">
         <v>65.6026</v>
       </c>
-      <c r="AB10" s="44" t="n">
+      <c r="AB10" s="48" t="n">
         <v>52.7499</v>
       </c>
-      <c r="AC10" s="44" t="n">
+      <c r="AC10" s="48" t="n">
         <v>56.5563</v>
       </c>
-      <c r="AD10" s="44" t="n">
+      <c r="AD10" s="48" t="n">
         <v>50.0815</v>
       </c>
-      <c r="AE10" s="44" t="n">
+      <c r="AE10" s="48" t="n">
         <v>45.9772</v>
       </c>
-      <c r="AF10" s="44" t="n">
+      <c r="AF10" s="48" t="n">
         <v>70.4145</v>
       </c>
-      <c r="AG10" s="44" t="n">
+      <c r="AG10" s="48" t="n">
         <v>50.0775</v>
       </c>
-      <c r="AH10" s="44" t="n">
+      <c r="AH10" s="48" t="n">
         <v>56.1356</v>
       </c>
-      <c r="AI10" s="44" t="inlineStr"/>
-      <c r="AJ10" s="44" t="n">
+      <c r="AI10" s="48" t="inlineStr"/>
+      <c r="AJ10" s="48" t="n">
         <v>50.5924</v>
       </c>
-      <c r="AK10" s="44" t="n">
+      <c r="AK10" s="48" t="n">
         <v>52.4193</v>
       </c>
-      <c r="AL10" s="44" t="n">
+      <c r="AL10" s="48" t="n">
         <v>51.7469</v>
       </c>
-      <c r="AM10" s="44" t="n">
+      <c r="AM10" s="48" t="n">
         <v>58.8231</v>
       </c>
-      <c r="AN10" s="44" t="n">
+      <c r="AN10" s="48" t="n">
         <v>47.725</v>
       </c>
-      <c r="AO10" s="44" t="inlineStr"/>
-      <c r="AP10" s="44" t="n">
+      <c r="AO10" s="48" t="inlineStr"/>
+      <c r="AP10" s="48" t="n">
         <v>53.1571</v>
       </c>
-      <c r="AQ10" s="44" t="n">
+      <c r="AQ10" s="48" t="n">
         <v>41.2855</v>
       </c>
-      <c r="AR10" s="44" t="n">
+      <c r="AR10" s="48" t="n">
         <v>60.6717</v>
       </c>
-      <c r="AS10" s="44" t="n">
+      <c r="AS10" s="48" t="n">
         <v>45.0033</v>
       </c>
-      <c r="AT10" s="44" t="n">
+      <c r="AT10" s="48" t="n">
         <v>45.9727</v>
       </c>
-      <c r="AU10" s="44" t="n">
+      <c r="AU10" s="48" t="n">
         <v>50.9844</v>
       </c>
-      <c r="AV10" s="44" t="n">
+      <c r="AV10" s="48" t="n">
         <v>53.3779</v>
       </c>
-      <c r="AW10" s="44" t="n">
+      <c r="AW10" s="48" t="n">
         <v>47.9339</v>
       </c>
-      <c r="AX10" s="44" t="inlineStr"/>
-      <c r="AY10" s="44" t="n">
+      <c r="AX10" s="48" t="inlineStr"/>
+      <c r="AY10" s="48" t="n">
         <v>48.9433</v>
       </c>
-      <c r="AZ10" s="44" t="n">
+      <c r="AZ10" s="48" t="n">
         <v>50.6582</v>
       </c>
-      <c r="BA10" s="44" t="n">
+      <c r="BA10" s="48" t="n">
         <v>47.0187</v>
       </c>
-      <c r="BB10" s="44" t="n">
+      <c r="BB10" s="48" t="n">
         <v>34.7826</v>
       </c>
-      <c r="BC10" s="44" t="inlineStr"/>
-      <c r="BD10" s="44" t="n">
+      <c r="BC10" s="48" t="inlineStr"/>
+      <c r="BD10" s="48" t="n">
         <v>46.9064</v>
       </c>
-      <c r="BE10" s="44" t="n">
+      <c r="BE10" s="48" t="n">
         <v>45.3534</v>
       </c>
-      <c r="BF10" s="44" t="n">
+      <c r="BF10" s="48" t="n">
         <v>37.4375</v>
       </c>
-      <c r="BG10" s="44" t="n">
+      <c r="BG10" s="48" t="n">
         <v>42.9454</v>
       </c>
-      <c r="BH10" s="44" t="inlineStr"/>
-      <c r="BI10" s="44" t="n">
+      <c r="BH10" s="48" t="inlineStr"/>
+      <c r="BI10" s="48" t="n">
         <v>48.9395</v>
       </c>
-      <c r="BJ10" s="44" t="n">
+      <c r="BJ10" s="48" t="n">
         <v>37.5879</v>
       </c>
-      <c r="BK10" s="44" t="inlineStr"/>
-      <c r="BL10" s="44" t="n">
+      <c r="BK10" s="48" t="inlineStr"/>
+      <c r="BL10" s="48" t="n">
         <v>24.1343</v>
       </c>
-      <c r="BM10" s="44" t="n">
+      <c r="BM10" s="48" t="n">
         <v>41.951</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr"/>
-      <c r="C11" s="44" t="n">
+      <c r="B11" s="48" t="inlineStr"/>
+      <c r="C11" s="48" t="n">
         <v>72.27</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="48" t="n">
         <v>72.5669</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="48" t="n">
         <v>73.791</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="48" t="n">
         <v>75.1631</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="48" t="n">
         <v>78.7362</v>
       </c>
-      <c r="H11" s="44" t="inlineStr"/>
-      <c r="I11" s="44" t="inlineStr"/>
-      <c r="J11" s="44" t="n">
+      <c r="H11" s="48" t="inlineStr"/>
+      <c r="I11" s="48" t="inlineStr"/>
+      <c r="J11" s="48" t="n">
         <v>73.3522</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="48" t="n">
         <v>65.4575</v>
       </c>
-      <c r="L11" s="44" t="n">
+      <c r="L11" s="48" t="n">
         <v>66.53019999999999</v>
       </c>
-      <c r="M11" s="44" t="inlineStr"/>
-      <c r="N11" s="44" t="n">
+      <c r="M11" s="48" t="inlineStr"/>
+      <c r="N11" s="48" t="n">
         <v>56.2814</v>
       </c>
-      <c r="O11" s="44" t="n">
+      <c r="O11" s="48" t="n">
         <v>71.5147</v>
       </c>
-      <c r="P11" s="44" t="n">
+      <c r="P11" s="48" t="n">
         <v>69.20489999999999</v>
       </c>
-      <c r="Q11" s="44" t="inlineStr"/>
-      <c r="R11" s="44" t="inlineStr"/>
-      <c r="S11" s="44" t="n">
+      <c r="Q11" s="48" t="inlineStr"/>
+      <c r="R11" s="48" t="inlineStr"/>
+      <c r="S11" s="48" t="n">
         <v>67.625</v>
       </c>
-      <c r="T11" s="44" t="inlineStr"/>
-      <c r="U11" s="44" t="n">
+      <c r="T11" s="48" t="inlineStr"/>
+      <c r="U11" s="48" t="n">
         <v>67.1048</v>
       </c>
-      <c r="V11" s="44" t="inlineStr"/>
-      <c r="W11" s="44" t="n">
+      <c r="V11" s="48" t="inlineStr"/>
+      <c r="W11" s="48" t="n">
         <v>72.065</v>
       </c>
-      <c r="X11" s="44" t="n">
+      <c r="X11" s="48" t="n">
         <v>68.9344</v>
       </c>
-      <c r="Y11" s="44" t="n">
+      <c r="Y11" s="48" t="n">
         <v>60.5357</v>
       </c>
-      <c r="Z11" s="44" t="n">
+      <c r="Z11" s="48" t="n">
         <v>55.6734</v>
       </c>
-      <c r="AA11" s="44" t="n">
+      <c r="AA11" s="48" t="n">
         <v>65.91679999999999</v>
       </c>
-      <c r="AB11" s="44" t="n">
+      <c r="AB11" s="48" t="n">
         <v>53.3239</v>
       </c>
-      <c r="AC11" s="44" t="n">
+      <c r="AC11" s="48" t="n">
         <v>57.4464</v>
       </c>
-      <c r="AD11" s="44" t="n">
+      <c r="AD11" s="48" t="n">
         <v>50.9901</v>
       </c>
-      <c r="AE11" s="44" t="n">
+      <c r="AE11" s="48" t="n">
         <v>46.5163</v>
       </c>
-      <c r="AF11" s="44" t="n">
+      <c r="AF11" s="48" t="n">
         <v>68.9449</v>
       </c>
-      <c r="AG11" s="44" t="n">
+      <c r="AG11" s="48" t="n">
         <v>50.4335</v>
       </c>
-      <c r="AH11" s="44" t="n">
+      <c r="AH11" s="48" t="n">
         <v>57.5594</v>
       </c>
-      <c r="AI11" s="44" t="inlineStr"/>
-      <c r="AJ11" s="44" t="n">
+      <c r="AI11" s="48" t="inlineStr"/>
+      <c r="AJ11" s="48" t="n">
         <v>57.3696</v>
       </c>
-      <c r="AK11" s="44" t="n">
+      <c r="AK11" s="48" t="n">
         <v>53.0711</v>
       </c>
-      <c r="AL11" s="44" t="n">
+      <c r="AL11" s="48" t="n">
         <v>54.4464</v>
       </c>
-      <c r="AM11" s="44" t="n">
+      <c r="AM11" s="48" t="n">
         <v>58.4618</v>
       </c>
-      <c r="AN11" s="44" t="n">
+      <c r="AN11" s="48" t="n">
         <v>48.6486</v>
       </c>
-      <c r="AO11" s="44" t="inlineStr"/>
-      <c r="AP11" s="44" t="n">
+      <c r="AO11" s="48" t="inlineStr"/>
+      <c r="AP11" s="48" t="n">
         <v>53.1369</v>
       </c>
-      <c r="AQ11" s="44" t="n">
+      <c r="AQ11" s="48" t="n">
         <v>43.4454</v>
       </c>
-      <c r="AR11" s="44" t="n">
+      <c r="AR11" s="48" t="n">
         <v>60.4838</v>
       </c>
-      <c r="AS11" s="44" t="n">
+      <c r="AS11" s="48" t="n">
         <v>46.6467</v>
       </c>
-      <c r="AT11" s="44" t="n">
+      <c r="AT11" s="48" t="n">
         <v>46.876</v>
       </c>
-      <c r="AU11" s="44" t="n">
+      <c r="AU11" s="48" t="n">
         <v>53.2783</v>
       </c>
-      <c r="AV11" s="44" t="n">
+      <c r="AV11" s="48" t="n">
         <v>49.6616</v>
       </c>
-      <c r="AW11" s="44" t="n">
+      <c r="AW11" s="48" t="n">
         <v>47.2056</v>
       </c>
-      <c r="AX11" s="44" t="inlineStr"/>
-      <c r="AY11" s="44" t="n">
+      <c r="AX11" s="48" t="inlineStr"/>
+      <c r="AY11" s="48" t="n">
         <v>46.3765</v>
       </c>
-      <c r="AZ11" s="44" t="n">
+      <c r="AZ11" s="48" t="n">
         <v>51.3888</v>
       </c>
-      <c r="BA11" s="44" t="n">
+      <c r="BA11" s="48" t="n">
         <v>50.3382</v>
       </c>
-      <c r="BB11" s="44" t="n">
+      <c r="BB11" s="48" t="n">
         <v>41.9294</v>
       </c>
-      <c r="BC11" s="44" t="inlineStr"/>
-      <c r="BD11" s="44" t="n">
+      <c r="BC11" s="48" t="inlineStr"/>
+      <c r="BD11" s="48" t="n">
         <v>46.9517</v>
       </c>
-      <c r="BE11" s="44" t="n">
+      <c r="BE11" s="48" t="n">
         <v>45.3338</v>
       </c>
-      <c r="BF11" s="44" t="n">
+      <c r="BF11" s="48" t="n">
         <v>37.913</v>
       </c>
-      <c r="BG11" s="44" t="n">
+      <c r="BG11" s="48" t="n">
         <v>43.1355</v>
       </c>
-      <c r="BH11" s="44" t="inlineStr"/>
-      <c r="BI11" s="44" t="n">
+      <c r="BH11" s="48" t="inlineStr"/>
+      <c r="BI11" s="48" t="n">
         <v>53.0851</v>
       </c>
-      <c r="BJ11" s="44" t="n">
+      <c r="BJ11" s="48" t="n">
         <v>37.9725</v>
       </c>
-      <c r="BK11" s="44" t="inlineStr"/>
-      <c r="BL11" s="44" t="n">
+      <c r="BK11" s="48" t="inlineStr"/>
+      <c r="BL11" s="48" t="n">
         <v>26.9266</v>
       </c>
-      <c r="BM11" s="44" t="n">
+      <c r="BM11" s="48" t="n">
         <v>39.033</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr"/>
-      <c r="C12" s="44" t="n">
+      <c r="B12" s="48" t="inlineStr"/>
+      <c r="C12" s="48" t="n">
         <v>71.4875</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="48" t="n">
         <v>70.8817</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="48" t="n">
         <v>72.34999999999999</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="48" t="n">
         <v>73.8514</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="48" t="n">
         <v>75.3955</v>
       </c>
-      <c r="H12" s="44" t="inlineStr"/>
-      <c r="I12" s="44" t="inlineStr"/>
-      <c r="J12" s="44" t="n">
+      <c r="H12" s="48" t="inlineStr"/>
+      <c r="I12" s="48" t="inlineStr"/>
+      <c r="J12" s="48" t="n">
         <v>72.313</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="48" t="n">
         <v>62.2872</v>
       </c>
-      <c r="L12" s="44" t="n">
+      <c r="L12" s="48" t="n">
         <v>69.55</v>
       </c>
-      <c r="M12" s="44" t="inlineStr"/>
-      <c r="N12" s="44" t="n">
+      <c r="M12" s="48" t="inlineStr"/>
+      <c r="N12" s="48" t="n">
         <v>53.8584</v>
       </c>
-      <c r="O12" s="44" t="n">
+      <c r="O12" s="48" t="n">
         <v>68.2174</v>
       </c>
-      <c r="P12" s="44" t="n">
+      <c r="P12" s="48" t="n">
         <v>67.3082</v>
       </c>
-      <c r="Q12" s="44" t="inlineStr"/>
-      <c r="R12" s="44" t="inlineStr"/>
-      <c r="S12" s="44" t="n">
+      <c r="Q12" s="48" t="inlineStr"/>
+      <c r="R12" s="48" t="inlineStr"/>
+      <c r="S12" s="48" t="n">
         <v>66.53270000000001</v>
       </c>
-      <c r="T12" s="44" t="inlineStr"/>
-      <c r="U12" s="44" t="n">
+      <c r="T12" s="48" t="inlineStr"/>
+      <c r="U12" s="48" t="n">
         <v>65.74299999999999</v>
       </c>
-      <c r="V12" s="44" t="inlineStr"/>
-      <c r="W12" s="44" t="n">
+      <c r="V12" s="48" t="inlineStr"/>
+      <c r="W12" s="48" t="n">
         <v>66.8361</v>
       </c>
-      <c r="X12" s="44" t="n">
+      <c r="X12" s="48" t="n">
         <v>64.5579</v>
       </c>
-      <c r="Y12" s="44" t="n">
+      <c r="Y12" s="48" t="n">
         <v>56.9106</v>
       </c>
-      <c r="Z12" s="44" t="n">
+      <c r="Z12" s="48" t="n">
         <v>53.7152</v>
       </c>
-      <c r="AA12" s="44" t="n">
+      <c r="AA12" s="48" t="n">
         <v>62.2934</v>
       </c>
-      <c r="AB12" s="44" t="n">
+      <c r="AB12" s="48" t="n">
         <v>55.4995</v>
       </c>
-      <c r="AC12" s="44" t="n">
+      <c r="AC12" s="48" t="n">
         <v>55.5723</v>
       </c>
-      <c r="AD12" s="44" t="n">
+      <c r="AD12" s="48" t="n">
         <v>48.3937</v>
       </c>
-      <c r="AE12" s="44" t="n">
+      <c r="AE12" s="48" t="n">
         <v>50.7413</v>
       </c>
-      <c r="AF12" s="44" t="n">
+      <c r="AF12" s="48" t="n">
         <v>63.8795</v>
       </c>
-      <c r="AG12" s="44" t="n">
+      <c r="AG12" s="48" t="n">
         <v>49.5188</v>
       </c>
-      <c r="AH12" s="44" t="n">
+      <c r="AH12" s="48" t="n">
         <v>55.7576</v>
       </c>
-      <c r="AI12" s="44" t="inlineStr"/>
-      <c r="AJ12" s="44" t="n">
+      <c r="AI12" s="48" t="inlineStr"/>
+      <c r="AJ12" s="48" t="n">
         <v>56.3638</v>
       </c>
-      <c r="AK12" s="44" t="n">
+      <c r="AK12" s="48" t="n">
         <v>54.9426</v>
       </c>
-      <c r="AL12" s="44" t="n">
+      <c r="AL12" s="48" t="n">
         <v>53.3815</v>
       </c>
-      <c r="AM12" s="44" t="n">
+      <c r="AM12" s="48" t="n">
         <v>58.8018</v>
       </c>
-      <c r="AN12" s="44" t="n">
+      <c r="AN12" s="48" t="n">
         <v>48.3558</v>
       </c>
-      <c r="AO12" s="44" t="inlineStr"/>
-      <c r="AP12" s="44" t="n">
+      <c r="AO12" s="48" t="inlineStr"/>
+      <c r="AP12" s="48" t="n">
         <v>51.746</v>
       </c>
-      <c r="AQ12" s="44" t="n">
+      <c r="AQ12" s="48" t="n">
         <v>42.3697</v>
       </c>
-      <c r="AR12" s="44" t="n">
+      <c r="AR12" s="48" t="n">
         <v>58.907</v>
       </c>
-      <c r="AS12" s="44" t="n">
+      <c r="AS12" s="48" t="n">
         <v>49.1311</v>
       </c>
-      <c r="AT12" s="44" t="n">
+      <c r="AT12" s="48" t="n">
         <v>44.1731</v>
       </c>
-      <c r="AU12" s="44" t="n">
+      <c r="AU12" s="48" t="n">
         <v>48.2646</v>
       </c>
-      <c r="AV12" s="44" t="n">
+      <c r="AV12" s="48" t="n">
         <v>48.8618</v>
       </c>
-      <c r="AW12" s="44" t="n">
+      <c r="AW12" s="48" t="n">
         <v>44.2651</v>
       </c>
-      <c r="AX12" s="44" t="inlineStr"/>
-      <c r="AY12" s="44" t="n">
+      <c r="AX12" s="48" t="inlineStr"/>
+      <c r="AY12" s="48" t="n">
         <v>48.0326</v>
       </c>
-      <c r="AZ12" s="44" t="n">
+      <c r="AZ12" s="48" t="n">
         <v>49.0243</v>
       </c>
-      <c r="BA12" s="44" t="n">
+      <c r="BA12" s="48" t="n">
         <v>41.1205</v>
       </c>
-      <c r="BB12" s="44" t="n">
+      <c r="BB12" s="48" t="n">
         <v>39.8297</v>
       </c>
-      <c r="BC12" s="44" t="inlineStr"/>
-      <c r="BD12" s="44" t="n">
+      <c r="BC12" s="48" t="inlineStr"/>
+      <c r="BD12" s="48" t="n">
         <v>42.0465</v>
       </c>
-      <c r="BE12" s="44" t="n">
+      <c r="BE12" s="48" t="n">
         <v>41.1828</v>
       </c>
-      <c r="BF12" s="44" t="n">
+      <c r="BF12" s="48" t="n">
         <v>34.1693</v>
       </c>
-      <c r="BG12" s="44" t="n">
+      <c r="BG12" s="48" t="n">
         <v>42.3433</v>
       </c>
-      <c r="BH12" s="44" t="inlineStr"/>
-      <c r="BI12" s="44" t="n">
+      <c r="BH12" s="48" t="inlineStr"/>
+      <c r="BI12" s="48" t="n">
         <v>45.9367</v>
       </c>
-      <c r="BJ12" s="44" t="n">
+      <c r="BJ12" s="48" t="n">
         <v>33.4899</v>
       </c>
-      <c r="BK12" s="44" t="inlineStr"/>
-      <c r="BL12" s="44" t="n">
+      <c r="BK12" s="48" t="inlineStr"/>
+      <c r="BL12" s="48" t="n">
         <v>26.1342</v>
       </c>
-      <c r="BM12" s="44" t="n">
+      <c r="BM12" s="48" t="n">
         <v>33.3674</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr"/>
-      <c r="C13" s="44" t="n">
+      <c r="B13" s="48" t="inlineStr"/>
+      <c r="C13" s="48" t="n">
         <v>71.6455</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="48" t="n">
         <v>71.7663</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="48" t="n">
         <v>71.9795</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="48" t="n">
         <v>74.28189999999999</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="48" t="n">
         <v>74.4384</v>
       </c>
-      <c r="H13" s="44" t="inlineStr"/>
-      <c r="I13" s="44" t="inlineStr"/>
-      <c r="J13" s="44" t="n">
+      <c r="H13" s="48" t="inlineStr"/>
+      <c r="I13" s="48" t="inlineStr"/>
+      <c r="J13" s="48" t="n">
         <v>72.49120000000001</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="48" t="n">
         <v>65.3715</v>
       </c>
-      <c r="L13" s="44" t="n">
+      <c r="L13" s="48" t="n">
         <v>69.94240000000001</v>
       </c>
-      <c r="M13" s="44" t="inlineStr"/>
-      <c r="N13" s="44" t="n">
+      <c r="M13" s="48" t="inlineStr"/>
+      <c r="N13" s="48" t="n">
         <v>55.7471</v>
       </c>
-      <c r="O13" s="44" t="n">
+      <c r="O13" s="48" t="n">
         <v>67.242</v>
       </c>
-      <c r="P13" s="44" t="n">
+      <c r="P13" s="48" t="n">
         <v>68.6855</v>
       </c>
-      <c r="Q13" s="44" t="inlineStr"/>
-      <c r="R13" s="44" t="inlineStr"/>
-      <c r="S13" s="44" t="n">
+      <c r="Q13" s="48" t="inlineStr"/>
+      <c r="R13" s="48" t="inlineStr"/>
+      <c r="S13" s="48" t="n">
         <v>66.61239999999999</v>
       </c>
-      <c r="T13" s="44" t="inlineStr"/>
-      <c r="U13" s="44" t="n">
+      <c r="T13" s="48" t="inlineStr"/>
+      <c r="U13" s="48" t="n">
         <v>62.9984</v>
       </c>
-      <c r="V13" s="44" t="inlineStr"/>
-      <c r="W13" s="44" t="n">
+      <c r="V13" s="48" t="inlineStr"/>
+      <c r="W13" s="48" t="n">
         <v>67.6014</v>
       </c>
-      <c r="X13" s="44" t="n">
+      <c r="X13" s="48" t="n">
         <v>67.8729</v>
       </c>
-      <c r="Y13" s="44" t="n">
+      <c r="Y13" s="48" t="n">
         <v>56.7366</v>
       </c>
-      <c r="Z13" s="44" t="n">
+      <c r="Z13" s="48" t="n">
         <v>54.3581</v>
       </c>
-      <c r="AA13" s="44" t="n">
+      <c r="AA13" s="48" t="n">
         <v>62.5766</v>
       </c>
-      <c r="AB13" s="44" t="n">
+      <c r="AB13" s="48" t="n">
         <v>56.3971</v>
       </c>
-      <c r="AC13" s="44" t="n">
+      <c r="AC13" s="48" t="n">
         <v>56.0225</v>
       </c>
-      <c r="AD13" s="44" t="n">
+      <c r="AD13" s="48" t="n">
         <v>54.8994</v>
       </c>
-      <c r="AE13" s="44" t="n">
+      <c r="AE13" s="48" t="n">
         <v>50.7956</v>
       </c>
-      <c r="AF13" s="44" t="n">
+      <c r="AF13" s="48" t="n">
         <v>64.6788</v>
       </c>
-      <c r="AG13" s="44" t="n">
+      <c r="AG13" s="48" t="n">
         <v>50.7663</v>
       </c>
-      <c r="AH13" s="44" t="n">
+      <c r="AH13" s="48" t="n">
         <v>55.7646</v>
       </c>
-      <c r="AI13" s="44" t="inlineStr"/>
-      <c r="AJ13" s="44" t="n">
+      <c r="AI13" s="48" t="inlineStr"/>
+      <c r="AJ13" s="48" t="n">
         <v>58.2235</v>
       </c>
-      <c r="AK13" s="44" t="n">
+      <c r="AK13" s="48" t="n">
         <v>55.2946</v>
       </c>
-      <c r="AL13" s="44" t="n">
+      <c r="AL13" s="48" t="n">
         <v>53.6515</v>
       </c>
-      <c r="AM13" s="44" t="n">
+      <c r="AM13" s="48" t="n">
         <v>58.8468</v>
       </c>
-      <c r="AN13" s="44" t="n">
+      <c r="AN13" s="48" t="n">
         <v>48.6494</v>
       </c>
-      <c r="AO13" s="44" t="inlineStr"/>
-      <c r="AP13" s="44" t="n">
+      <c r="AO13" s="48" t="inlineStr"/>
+      <c r="AP13" s="48" t="n">
         <v>50.6955</v>
       </c>
-      <c r="AQ13" s="44" t="n">
+      <c r="AQ13" s="48" t="n">
         <v>43.8291</v>
       </c>
-      <c r="AR13" s="44" t="n">
+      <c r="AR13" s="48" t="n">
         <v>57.6643</v>
       </c>
-      <c r="AS13" s="44" t="n">
+      <c r="AS13" s="48" t="n">
         <v>51.4043</v>
       </c>
-      <c r="AT13" s="44" t="n">
+      <c r="AT13" s="48" t="n">
         <v>46.0408</v>
       </c>
-      <c r="AU13" s="44" t="n">
+      <c r="AU13" s="48" t="n">
         <v>47.9405</v>
       </c>
-      <c r="AV13" s="44" t="n">
+      <c r="AV13" s="48" t="n">
         <v>50.8908</v>
       </c>
-      <c r="AW13" s="44" t="n">
+      <c r="AW13" s="48" t="n">
         <v>42.9582</v>
       </c>
-      <c r="AX13" s="44" t="inlineStr"/>
-      <c r="AY13" s="44" t="n">
+      <c r="AX13" s="48" t="inlineStr"/>
+      <c r="AY13" s="48" t="n">
         <v>51.8224</v>
       </c>
-      <c r="AZ13" s="44" t="n">
+      <c r="AZ13" s="48" t="n">
         <v>47.2223</v>
       </c>
-      <c r="BA13" s="44" t="n">
+      <c r="BA13" s="48" t="n">
         <v>44.8968</v>
       </c>
-      <c r="BB13" s="44" t="n">
+      <c r="BB13" s="48" t="n">
         <v>41.0483</v>
       </c>
-      <c r="BC13" s="44" t="inlineStr"/>
-      <c r="BD13" s="44" t="n">
+      <c r="BC13" s="48" t="inlineStr"/>
+      <c r="BD13" s="48" t="n">
         <v>40.3168</v>
       </c>
-      <c r="BE13" s="44" t="n">
+      <c r="BE13" s="48" t="n">
         <v>42.3946</v>
       </c>
-      <c r="BF13" s="44" t="n">
+      <c r="BF13" s="48" t="n">
         <v>36.131</v>
       </c>
-      <c r="BG13" s="44" t="n">
+      <c r="BG13" s="48" t="n">
         <v>41.4681</v>
       </c>
-      <c r="BH13" s="44" t="inlineStr"/>
-      <c r="BI13" s="44" t="n">
+      <c r="BH13" s="48" t="inlineStr"/>
+      <c r="BI13" s="48" t="n">
         <v>47.4718</v>
       </c>
-      <c r="BJ13" s="44" t="n">
+      <c r="BJ13" s="48" t="n">
         <v>33.1982</v>
       </c>
-      <c r="BK13" s="44" t="inlineStr"/>
-      <c r="BL13" s="44" t="n">
+      <c r="BK13" s="48" t="inlineStr"/>
+      <c r="BL13" s="48" t="n">
         <v>28.7116</v>
       </c>
-      <c r="BM13" s="44" t="n">
+      <c r="BM13" s="48" t="n">
         <v>35.9051</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B14" s="44" t="n">
+      <c r="B14" s="48" t="n">
         <v>59.9693</v>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="48" t="n">
         <v>71.9044</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="48" t="n">
         <v>71.7983</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="48" t="n">
         <v>71.0219</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="48" t="n">
         <v>74.229</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="48" t="n">
         <v>73.4825</v>
       </c>
-      <c r="H14" s="44" t="n">
+      <c r="H14" s="48" t="n">
         <v>65.7359</v>
       </c>
-      <c r="I14" s="44" t="n">
+      <c r="I14" s="48" t="n">
         <v>74.029</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J14" s="48" t="n">
         <v>70.4881</v>
       </c>
-      <c r="K14" s="44" t="n">
+      <c r="K14" s="48" t="n">
         <v>62.8364</v>
       </c>
-      <c r="L14" s="44" t="n">
+      <c r="L14" s="48" t="n">
         <v>67.7381</v>
       </c>
-      <c r="M14" s="44" t="inlineStr"/>
-      <c r="N14" s="44" t="n">
+      <c r="M14" s="48" t="inlineStr"/>
+      <c r="N14" s="48" t="n">
         <v>52.9822</v>
       </c>
-      <c r="O14" s="44" t="n">
+      <c r="O14" s="48" t="n">
         <v>66.03789999999999</v>
       </c>
-      <c r="P14" s="44" t="n">
+      <c r="P14" s="48" t="n">
         <v>68.6251</v>
       </c>
-      <c r="Q14" s="44" t="n">
+      <c r="Q14" s="48" t="n">
         <v>65.6198</v>
       </c>
-      <c r="R14" s="44" t="n">
+      <c r="R14" s="48" t="n">
         <v>58.8464</v>
       </c>
-      <c r="S14" s="44" t="n">
+      <c r="S14" s="48" t="n">
         <v>66.8292</v>
       </c>
-      <c r="T14" s="44" t="n">
+      <c r="T14" s="48" t="n">
         <v>55.3959</v>
       </c>
-      <c r="U14" s="44" t="n">
+      <c r="U14" s="48" t="n">
         <v>64.69750000000001</v>
       </c>
-      <c r="V14" s="44" t="n">
+      <c r="V14" s="48" t="n">
         <v>58.252</v>
       </c>
-      <c r="W14" s="44" t="n">
+      <c r="W14" s="48" t="n">
         <v>66.4975</v>
       </c>
-      <c r="X14" s="44" t="n">
+      <c r="X14" s="48" t="n">
         <v>60.1469</v>
       </c>
-      <c r="Y14" s="44" t="n">
+      <c r="Y14" s="48" t="n">
         <v>56.4506</v>
       </c>
-      <c r="Z14" s="44" t="n">
+      <c r="Z14" s="48" t="n">
         <v>54.1569</v>
       </c>
-      <c r="AA14" s="44" t="n">
+      <c r="AA14" s="48" t="n">
         <v>64.5566</v>
       </c>
-      <c r="AB14" s="44" t="n">
+      <c r="AB14" s="48" t="n">
         <v>56.5023</v>
       </c>
-      <c r="AC14" s="44" t="n">
+      <c r="AC14" s="48" t="n">
         <v>55.3927</v>
       </c>
-      <c r="AD14" s="44" t="n">
+      <c r="AD14" s="48" t="n">
         <v>50.7567</v>
       </c>
-      <c r="AE14" s="44" t="n">
+      <c r="AE14" s="48" t="n">
         <v>52.142</v>
       </c>
-      <c r="AF14" s="44" t="n">
+      <c r="AF14" s="48" t="n">
         <v>60.2487</v>
       </c>
-      <c r="AG14" s="44" t="n">
+      <c r="AG14" s="48" t="n">
         <v>52.086</v>
       </c>
-      <c r="AH14" s="44" t="n">
+      <c r="AH14" s="48" t="n">
         <v>54.7396</v>
       </c>
-      <c r="AI14" s="44" t="n">
+      <c r="AI14" s="48" t="n">
         <v>48.3689</v>
       </c>
-      <c r="AJ14" s="44" t="n">
+      <c r="AJ14" s="48" t="n">
         <v>55.7993</v>
       </c>
-      <c r="AK14" s="44" t="n">
+      <c r="AK14" s="48" t="n">
         <v>55.6765</v>
       </c>
-      <c r="AL14" s="44" t="n">
+      <c r="AL14" s="48" t="n">
         <v>52.5528</v>
       </c>
-      <c r="AM14" s="44" t="n">
+      <c r="AM14" s="48" t="n">
         <v>59.5409</v>
       </c>
-      <c r="AN14" s="44" t="n">
+      <c r="AN14" s="48" t="n">
         <v>50.0942</v>
       </c>
-      <c r="AO14" s="44" t="n">
+      <c r="AO14" s="48" t="n">
         <v>50.0977</v>
       </c>
-      <c r="AP14" s="44" t="n">
+      <c r="AP14" s="48" t="n">
         <v>49.7082</v>
       </c>
-      <c r="AQ14" s="44" t="n">
+      <c r="AQ14" s="48" t="n">
         <v>42.7779</v>
       </c>
-      <c r="AR14" s="44" t="n">
+      <c r="AR14" s="48" t="n">
         <v>57.3032</v>
       </c>
-      <c r="AS14" s="44" t="n">
+      <c r="AS14" s="48" t="n">
         <v>49.3136</v>
       </c>
-      <c r="AT14" s="44" t="n">
+      <c r="AT14" s="48" t="n">
         <v>44.6895</v>
       </c>
-      <c r="AU14" s="44" t="n">
+      <c r="AU14" s="48" t="n">
         <v>45.7338</v>
       </c>
-      <c r="AV14" s="44" t="n">
+      <c r="AV14" s="48" t="n">
         <v>49.7863</v>
       </c>
-      <c r="AW14" s="44" t="n">
+      <c r="AW14" s="48" t="n">
         <v>42.4896</v>
       </c>
-      <c r="AX14" s="44" t="inlineStr"/>
-      <c r="AY14" s="44" t="n">
+      <c r="AX14" s="48" t="inlineStr"/>
+      <c r="AY14" s="48" t="n">
         <v>48.8345</v>
       </c>
-      <c r="AZ14" s="44" t="n">
+      <c r="AZ14" s="48" t="n">
         <v>46.752</v>
       </c>
-      <c r="BA14" s="44" t="n">
+      <c r="BA14" s="48" t="n">
         <v>40.6869</v>
       </c>
-      <c r="BB14" s="44" t="n">
+      <c r="BB14" s="48" t="n">
         <v>40.8672</v>
       </c>
-      <c r="BC14" s="44" t="n">
+      <c r="BC14" s="48" t="n">
         <v>42.3689</v>
       </c>
-      <c r="BD14" s="44" t="n">
+      <c r="BD14" s="48" t="n">
         <v>41.4712</v>
       </c>
-      <c r="BE14" s="44" t="n">
+      <c r="BE14" s="48" t="n">
         <v>38.5857</v>
       </c>
-      <c r="BF14" s="44" t="n">
+      <c r="BF14" s="48" t="n">
         <v>34.8653</v>
       </c>
-      <c r="BG14" s="44" t="n">
+      <c r="BG14" s="48" t="n">
         <v>43.018</v>
       </c>
-      <c r="BH14" s="44" t="n">
+      <c r="BH14" s="48" t="n">
         <v>37.8105</v>
       </c>
-      <c r="BI14" s="44" t="n">
+      <c r="BI14" s="48" t="n">
         <v>44.6082</v>
       </c>
-      <c r="BJ14" s="44" t="n">
+      <c r="BJ14" s="48" t="n">
         <v>30.7042</v>
       </c>
-      <c r="BK14" s="44" t="n">
+      <c r="BK14" s="48" t="n">
         <v>39.8344</v>
       </c>
-      <c r="BL14" s="44" t="n">
+      <c r="BL14" s="48" t="n">
         <v>27.2296</v>
       </c>
-      <c r="BM14" s="44" t="n">
+      <c r="BM14" s="48" t="n">
         <v>31.1011</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="48" t="n">
         <v>56.8665</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="48" t="n">
         <v>71.7366</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="48" t="n">
         <v>71.87439999999999</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="48" t="n">
         <v>70.9628</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="48" t="n">
         <v>74.83629999999999</v>
       </c>
-      <c r="G15" s="44" t="n">
+      <c r="G15" s="48" t="n">
         <v>73.4406</v>
       </c>
-      <c r="H15" s="44" t="n">
+      <c r="H15" s="48" t="n">
         <v>64.3605</v>
       </c>
-      <c r="I15" s="44" t="n">
+      <c r="I15" s="48" t="n">
         <v>72.0685</v>
       </c>
-      <c r="J15" s="44" t="n">
+      <c r="J15" s="48" t="n">
         <v>70.92100000000001</v>
       </c>
-      <c r="K15" s="44" t="n">
+      <c r="K15" s="48" t="n">
         <v>63.3457</v>
       </c>
-      <c r="L15" s="44" t="n">
+      <c r="L15" s="48" t="n">
         <v>68.80410000000001</v>
       </c>
-      <c r="M15" s="44" t="inlineStr"/>
-      <c r="N15" s="44" t="n">
+      <c r="M15" s="48" t="inlineStr"/>
+      <c r="N15" s="48" t="n">
         <v>52.5837</v>
       </c>
-      <c r="O15" s="44" t="n">
+      <c r="O15" s="48" t="n">
         <v>66.3853</v>
       </c>
-      <c r="P15" s="44" t="n">
+      <c r="P15" s="48" t="n">
         <v>67.9879</v>
       </c>
-      <c r="Q15" s="44" t="n">
+      <c r="Q15" s="48" t="n">
         <v>65.01779999999999</v>
       </c>
-      <c r="R15" s="44" t="n">
+      <c r="R15" s="48" t="n">
         <v>59.7617</v>
       </c>
-      <c r="S15" s="44" t="n">
+      <c r="S15" s="48" t="n">
         <v>66.42319999999999</v>
       </c>
-      <c r="T15" s="44" t="n">
+      <c r="T15" s="48" t="n">
         <v>51.6274</v>
       </c>
-      <c r="U15" s="44" t="n">
+      <c r="U15" s="48" t="n">
         <v>64.7975</v>
       </c>
-      <c r="V15" s="44" t="n">
+      <c r="V15" s="48" t="n">
         <v>57.9208</v>
       </c>
-      <c r="W15" s="44" t="n">
+      <c r="W15" s="48" t="n">
         <v>66.4111</v>
       </c>
-      <c r="X15" s="44" t="n">
+      <c r="X15" s="48" t="n">
         <v>60.0818</v>
       </c>
-      <c r="Y15" s="44" t="n">
+      <c r="Y15" s="48" t="n">
         <v>54.4827</v>
       </c>
-      <c r="Z15" s="44" t="n">
+      <c r="Z15" s="48" t="n">
         <v>53.809</v>
       </c>
-      <c r="AA15" s="44" t="n">
+      <c r="AA15" s="48" t="n">
         <v>66.2272</v>
       </c>
-      <c r="AB15" s="44" t="n">
+      <c r="AB15" s="48" t="n">
         <v>56.469</v>
       </c>
-      <c r="AC15" s="44" t="n">
+      <c r="AC15" s="48" t="n">
         <v>54.6529</v>
       </c>
-      <c r="AD15" s="44" t="n">
+      <c r="AD15" s="48" t="n">
         <v>55.2364</v>
       </c>
-      <c r="AE15" s="44" t="n">
+      <c r="AE15" s="48" t="n">
         <v>53.3282</v>
       </c>
-      <c r="AF15" s="44" t="n">
+      <c r="AF15" s="48" t="n">
         <v>57.4622</v>
       </c>
-      <c r="AG15" s="44" t="n">
+      <c r="AG15" s="48" t="n">
         <v>52.157</v>
       </c>
-      <c r="AH15" s="44" t="n">
+      <c r="AH15" s="48" t="n">
         <v>54.8382</v>
       </c>
-      <c r="AI15" s="44" t="n">
+      <c r="AI15" s="48" t="n">
         <v>48.3597</v>
       </c>
-      <c r="AJ15" s="44" t="n">
+      <c r="AJ15" s="48" t="n">
         <v>56.6278</v>
       </c>
-      <c r="AK15" s="44" t="n">
+      <c r="AK15" s="48" t="n">
         <v>56.1571</v>
       </c>
-      <c r="AL15" s="44" t="n">
+      <c r="AL15" s="48" t="n">
         <v>53.7045</v>
       </c>
-      <c r="AM15" s="44" t="n">
+      <c r="AM15" s="48" t="n">
         <v>59.1131</v>
       </c>
-      <c r="AN15" s="44" t="n">
+      <c r="AN15" s="48" t="n">
         <v>51.2511</v>
       </c>
-      <c r="AO15" s="44" t="n">
+      <c r="AO15" s="48" t="n">
         <v>49.5154</v>
       </c>
-      <c r="AP15" s="44" t="n">
+      <c r="AP15" s="48" t="n">
         <v>51.7787</v>
       </c>
-      <c r="AQ15" s="44" t="n">
+      <c r="AQ15" s="48" t="n">
         <v>43.7772</v>
       </c>
-      <c r="AR15" s="44" t="n">
+      <c r="AR15" s="48" t="n">
         <v>56.7684</v>
       </c>
-      <c r="AS15" s="44" t="n">
+      <c r="AS15" s="48" t="n">
         <v>49.4137</v>
       </c>
-      <c r="AT15" s="44" t="n">
+      <c r="AT15" s="48" t="n">
         <v>44.2035</v>
       </c>
-      <c r="AU15" s="44" t="n">
+      <c r="AU15" s="48" t="n">
         <v>45.9375</v>
       </c>
-      <c r="AV15" s="44" t="n">
+      <c r="AV15" s="48" t="n">
         <v>50.4746</v>
       </c>
-      <c r="AW15" s="44" t="n">
+      <c r="AW15" s="48" t="n">
         <v>42.4886</v>
       </c>
-      <c r="AX15" s="44" t="inlineStr"/>
-      <c r="AY15" s="44" t="n">
+      <c r="AX15" s="48" t="inlineStr"/>
+      <c r="AY15" s="48" t="n">
         <v>48.265</v>
       </c>
-      <c r="AZ15" s="44" t="n">
+      <c r="AZ15" s="48" t="n">
         <v>46.5532</v>
       </c>
-      <c r="BA15" s="44" t="n">
+      <c r="BA15" s="48" t="n">
         <v>39.2139</v>
       </c>
-      <c r="BB15" s="44" t="n">
+      <c r="BB15" s="48" t="n">
         <v>38.387</v>
       </c>
-      <c r="BC15" s="44" t="n">
+      <c r="BC15" s="48" t="n">
         <v>42.4076</v>
       </c>
-      <c r="BD15" s="44" t="n">
+      <c r="BD15" s="48" t="n">
         <v>40.5793</v>
       </c>
-      <c r="BE15" s="44" t="n">
+      <c r="BE15" s="48" t="n">
         <v>37.0752</v>
       </c>
-      <c r="BF15" s="44" t="n">
+      <c r="BF15" s="48" t="n">
         <v>35.964</v>
       </c>
-      <c r="BG15" s="44" t="n">
+      <c r="BG15" s="48" t="n">
         <v>43.447</v>
       </c>
-      <c r="BH15" s="44" t="n">
+      <c r="BH15" s="48" t="n">
         <v>37.8727</v>
       </c>
-      <c r="BI15" s="44" t="n">
+      <c r="BI15" s="48" t="n">
         <v>44.0469</v>
       </c>
-      <c r="BJ15" s="44" t="n">
+      <c r="BJ15" s="48" t="n">
         <v>30.6929</v>
       </c>
-      <c r="BK15" s="44" t="n">
+      <c r="BK15" s="48" t="n">
         <v>36.7427</v>
       </c>
-      <c r="BL15" s="44" t="n">
+      <c r="BL15" s="48" t="n">
         <v>28.3535</v>
       </c>
-      <c r="BM15" s="44" t="n">
+      <c r="BM15" s="48" t="n">
         <v>30.7399</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="48" t="n">
         <v>63.5087</v>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C16" s="48" t="n">
         <v>65.9449</v>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="48" t="n">
         <v>66.3096</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="48" t="n">
         <v>65.8502</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="48" t="n">
         <v>65.1512</v>
       </c>
-      <c r="G16" s="44" t="n">
+      <c r="G16" s="48" t="n">
         <v>65.32989999999999</v>
       </c>
-      <c r="H16" s="44" t="n">
+      <c r="H16" s="48" t="n">
         <v>61.6248</v>
       </c>
-      <c r="I16" s="44" t="n">
+      <c r="I16" s="48" t="n">
         <v>61.1984</v>
       </c>
-      <c r="J16" s="44" t="n">
+      <c r="J16" s="48" t="n">
         <v>65.2547</v>
       </c>
-      <c r="K16" s="44" t="n">
+      <c r="K16" s="48" t="n">
         <v>61.1843</v>
       </c>
-      <c r="L16" s="44" t="n">
+      <c r="L16" s="48" t="n">
         <v>59.2495</v>
       </c>
-      <c r="M16" s="44" t="inlineStr"/>
-      <c r="N16" s="44" t="n">
+      <c r="M16" s="48" t="inlineStr"/>
+      <c r="N16" s="48" t="n">
         <v>55.9414</v>
       </c>
-      <c r="O16" s="44" t="n">
+      <c r="O16" s="48" t="n">
         <v>61.0779</v>
       </c>
-      <c r="P16" s="44" t="n">
+      <c r="P16" s="48" t="n">
         <v>58.8282</v>
       </c>
-      <c r="Q16" s="44" t="n">
+      <c r="Q16" s="48" t="n">
         <v>56.5866</v>
       </c>
-      <c r="R16" s="44" t="n">
+      <c r="R16" s="48" t="n">
         <v>59.4937</v>
       </c>
-      <c r="S16" s="44" t="n">
+      <c r="S16" s="48" t="n">
         <v>55.4994</v>
       </c>
-      <c r="T16" s="44" t="n">
+      <c r="T16" s="48" t="n">
         <v>55.4462</v>
       </c>
-      <c r="U16" s="44" t="n">
+      <c r="U16" s="48" t="n">
         <v>61.9023</v>
       </c>
-      <c r="V16" s="44" t="n">
+      <c r="V16" s="48" t="n">
         <v>54.4874</v>
       </c>
-      <c r="W16" s="44" t="n">
+      <c r="W16" s="48" t="n">
         <v>55.0981</v>
       </c>
-      <c r="X16" s="44" t="n">
+      <c r="X16" s="48" t="n">
         <v>53.7888</v>
       </c>
-      <c r="Y16" s="44" t="n">
+      <c r="Y16" s="48" t="n">
         <v>50.0956</v>
       </c>
-      <c r="Z16" s="44" t="n">
+      <c r="Z16" s="48" t="n">
         <v>52.3585</v>
       </c>
-      <c r="AA16" s="44" t="n">
+      <c r="AA16" s="48" t="n">
         <v>52.0649</v>
       </c>
-      <c r="AB16" s="44" t="n">
+      <c r="AB16" s="48" t="n">
         <v>51.2596</v>
       </c>
-      <c r="AC16" s="44" t="n">
+      <c r="AC16" s="48" t="n">
         <v>53.201</v>
       </c>
-      <c r="AD16" s="44" t="n">
+      <c r="AD16" s="48" t="n">
         <v>49.0948</v>
       </c>
-      <c r="AE16" s="44" t="n">
+      <c r="AE16" s="48" t="n">
         <v>45.7888</v>
       </c>
-      <c r="AF16" s="44" t="n">
+      <c r="AF16" s="48" t="n">
         <v>53.0602</v>
       </c>
-      <c r="AG16" s="44" t="n">
+      <c r="AG16" s="48" t="n">
         <v>49.8176</v>
       </c>
-      <c r="AH16" s="44" t="n">
+      <c r="AH16" s="48" t="n">
         <v>48.1755</v>
       </c>
-      <c r="AI16" s="44" t="n">
+      <c r="AI16" s="48" t="n">
         <v>45.8343</v>
       </c>
-      <c r="AJ16" s="44" t="n">
+      <c r="AJ16" s="48" t="n">
         <v>47.25</v>
       </c>
-      <c r="AK16" s="44" t="n">
+      <c r="AK16" s="48" t="n">
         <v>46.3321</v>
       </c>
-      <c r="AL16" s="44" t="n">
+      <c r="AL16" s="48" t="n">
         <v>49.4648</v>
       </c>
-      <c r="AM16" s="44" t="n">
+      <c r="AM16" s="48" t="n">
         <v>45.2597</v>
       </c>
-      <c r="AN16" s="44" t="n">
+      <c r="AN16" s="48" t="n">
         <v>46.03</v>
       </c>
-      <c r="AO16" s="44" t="n">
+      <c r="AO16" s="48" t="n">
         <v>47.4803</v>
       </c>
-      <c r="AP16" s="44" t="n">
+      <c r="AP16" s="48" t="n">
         <v>46.7427</v>
       </c>
-      <c r="AQ16" s="44" t="n">
+      <c r="AQ16" s="48" t="n">
         <v>43.674</v>
       </c>
-      <c r="AR16" s="44" t="n">
+      <c r="AR16" s="48" t="n">
         <v>50.0991</v>
       </c>
-      <c r="AS16" s="44" t="n">
+      <c r="AS16" s="48" t="n">
         <v>46.3035</v>
       </c>
-      <c r="AT16" s="44" t="n">
+      <c r="AT16" s="48" t="n">
         <v>41.8481</v>
       </c>
-      <c r="AU16" s="44" t="n">
+      <c r="AU16" s="48" t="n">
         <v>40.7387</v>
       </c>
-      <c r="AV16" s="44" t="n">
+      <c r="AV16" s="48" t="n">
         <v>42.0382</v>
       </c>
-      <c r="AW16" s="44" t="n">
+      <c r="AW16" s="48" t="n">
         <v>41.0062</v>
       </c>
-      <c r="AX16" s="44" t="n">
+      <c r="AX16" s="48" t="n">
         <v>48.0721</v>
       </c>
-      <c r="AY16" s="44" t="n">
+      <c r="AY16" s="48" t="n">
         <v>36.5323</v>
       </c>
-      <c r="AZ16" s="44" t="n">
+      <c r="AZ16" s="48" t="n">
         <v>44.6266</v>
       </c>
-      <c r="BA16" s="44" t="n">
+      <c r="BA16" s="48" t="n">
         <v>36.1488</v>
       </c>
-      <c r="BB16" s="44" t="n">
+      <c r="BB16" s="48" t="n">
         <v>36.9219</v>
       </c>
-      <c r="BC16" s="44" t="n">
+      <c r="BC16" s="48" t="n">
         <v>37.8405</v>
       </c>
-      <c r="BD16" s="44" t="n">
+      <c r="BD16" s="48" t="n">
         <v>36.6715</v>
       </c>
-      <c r="BE16" s="44" t="n">
+      <c r="BE16" s="48" t="n">
         <v>34.5029</v>
       </c>
-      <c r="BF16" s="44" t="n">
+      <c r="BF16" s="48" t="n">
         <v>27.6629</v>
       </c>
-      <c r="BG16" s="44" t="n">
+      <c r="BG16" s="48" t="n">
         <v>33.3293</v>
       </c>
-      <c r="BH16" s="44" t="n">
+      <c r="BH16" s="48" t="n">
         <v>31.6243</v>
       </c>
-      <c r="BI16" s="44" t="n">
+      <c r="BI16" s="48" t="n">
         <v>33.1138</v>
       </c>
-      <c r="BJ16" s="44" t="n">
+      <c r="BJ16" s="48" t="n">
         <v>26.5911</v>
       </c>
-      <c r="BK16" s="44" t="n">
+      <c r="BK16" s="48" t="n">
         <v>26.6317</v>
       </c>
-      <c r="BL16" s="44" t="n">
+      <c r="BL16" s="48" t="n">
         <v>20.2754</v>
       </c>
-      <c r="BM16" s="44" t="n">
+      <c r="BM16" s="48" t="n">
         <v>17.4846</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="48" t="n">
         <v>61.5166</v>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="48" t="n">
         <v>65.85980000000001</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="48" t="n">
         <v>65.03449999999999</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="48" t="n">
         <v>63.3148</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="48" t="n">
         <v>62.7429</v>
       </c>
-      <c r="G17" s="44" t="n">
+      <c r="G17" s="48" t="n">
         <v>64.7274</v>
       </c>
-      <c r="H17" s="44" t="n">
+      <c r="H17" s="48" t="n">
         <v>61.6623</v>
       </c>
-      <c r="I17" s="44" t="n">
+      <c r="I17" s="48" t="n">
         <v>62.1232</v>
       </c>
-      <c r="J17" s="44" t="n">
+      <c r="J17" s="48" t="n">
         <v>62.7889</v>
       </c>
-      <c r="K17" s="44" t="n">
+      <c r="K17" s="48" t="n">
         <v>59.7323</v>
       </c>
-      <c r="L17" s="44" t="n">
+      <c r="L17" s="48" t="n">
         <v>59.2118</v>
       </c>
-      <c r="M17" s="44" t="inlineStr"/>
-      <c r="N17" s="44" t="n">
+      <c r="M17" s="48" t="inlineStr"/>
+      <c r="N17" s="48" t="n">
         <v>56.699</v>
       </c>
-      <c r="O17" s="44" t="n">
+      <c r="O17" s="48" t="n">
         <v>59.8924</v>
       </c>
-      <c r="P17" s="44" t="n">
+      <c r="P17" s="48" t="n">
         <v>55.6058</v>
       </c>
-      <c r="Q17" s="44" t="n">
+      <c r="Q17" s="48" t="n">
         <v>58.2431</v>
       </c>
-      <c r="R17" s="44" t="n">
+      <c r="R17" s="48" t="n">
         <v>58.1723</v>
       </c>
-      <c r="S17" s="44" t="n">
+      <c r="S17" s="48" t="n">
         <v>54.0661</v>
       </c>
-      <c r="T17" s="44" t="n">
+      <c r="T17" s="48" t="n">
         <v>54.8396</v>
       </c>
-      <c r="U17" s="44" t="n">
+      <c r="U17" s="48" t="n">
         <v>61.7663</v>
       </c>
-      <c r="V17" s="44" t="n">
+      <c r="V17" s="48" t="n">
         <v>55.002</v>
       </c>
-      <c r="W17" s="44" t="n">
+      <c r="W17" s="48" t="n">
         <v>53.2541</v>
       </c>
-      <c r="X17" s="44" t="n">
+      <c r="X17" s="48" t="n">
         <v>52.7245</v>
       </c>
-      <c r="Y17" s="44" t="n">
+      <c r="Y17" s="48" t="n">
         <v>52.0003</v>
       </c>
-      <c r="Z17" s="44" t="n">
+      <c r="Z17" s="48" t="n">
         <v>53.7963</v>
       </c>
-      <c r="AA17" s="44" t="n">
+      <c r="AA17" s="48" t="n">
         <v>52.393</v>
       </c>
-      <c r="AB17" s="44" t="n">
+      <c r="AB17" s="48" t="n">
         <v>52.7219</v>
       </c>
-      <c r="AC17" s="44" t="n">
+      <c r="AC17" s="48" t="n">
         <v>51.137</v>
       </c>
-      <c r="AD17" s="44" t="n">
+      <c r="AD17" s="48" t="n">
         <v>46.8901</v>
       </c>
-      <c r="AE17" s="44" t="n">
+      <c r="AE17" s="48" t="n">
         <v>43.9419</v>
       </c>
-      <c r="AF17" s="44" t="n">
+      <c r="AF17" s="48" t="n">
         <v>49.344</v>
       </c>
-      <c r="AG17" s="44" t="n">
+      <c r="AG17" s="48" t="n">
         <v>47.4824</v>
       </c>
-      <c r="AH17" s="44" t="n">
+      <c r="AH17" s="48" t="n">
         <v>46.3531</v>
       </c>
-      <c r="AI17" s="44" t="n">
+      <c r="AI17" s="48" t="n">
         <v>46.126</v>
       </c>
-      <c r="AJ17" s="44" t="n">
+      <c r="AJ17" s="48" t="n">
         <v>47.2632</v>
       </c>
-      <c r="AK17" s="44" t="n">
+      <c r="AK17" s="48" t="n">
         <v>46.5192</v>
       </c>
-      <c r="AL17" s="44" t="n">
+      <c r="AL17" s="48" t="n">
         <v>49.2827</v>
       </c>
-      <c r="AM17" s="44" t="n">
+      <c r="AM17" s="48" t="n">
         <v>46.8888</v>
       </c>
-      <c r="AN17" s="44" t="n">
+      <c r="AN17" s="48" t="n">
         <v>45.747</v>
       </c>
-      <c r="AO17" s="44" t="n">
+      <c r="AO17" s="48" t="n">
         <v>47.4339</v>
       </c>
-      <c r="AP17" s="44" t="n">
+      <c r="AP17" s="48" t="n">
         <v>46.1474</v>
       </c>
-      <c r="AQ17" s="44" t="n">
+      <c r="AQ17" s="48" t="n">
         <v>44.4721</v>
       </c>
-      <c r="AR17" s="44" t="n">
+      <c r="AR17" s="48" t="n">
         <v>50.1108</v>
       </c>
-      <c r="AS17" s="44" t="n">
+      <c r="AS17" s="48" t="n">
         <v>44.2309</v>
       </c>
-      <c r="AT17" s="44" t="n">
+      <c r="AT17" s="48" t="n">
         <v>41.0915</v>
       </c>
-      <c r="AU17" s="44" t="n">
+      <c r="AU17" s="48" t="n">
         <v>41.4631</v>
       </c>
-      <c r="AV17" s="44" t="n">
+      <c r="AV17" s="48" t="n">
         <v>41.1133</v>
       </c>
-      <c r="AW17" s="44" t="n">
+      <c r="AW17" s="48" t="n">
         <v>41.7516</v>
       </c>
-      <c r="AX17" s="44" t="n">
+      <c r="AX17" s="48" t="n">
         <v>44.9437</v>
       </c>
-      <c r="AY17" s="44" t="n">
+      <c r="AY17" s="48" t="n">
         <v>36.6632</v>
       </c>
-      <c r="AZ17" s="44" t="n">
+      <c r="AZ17" s="48" t="n">
         <v>42.3468</v>
       </c>
-      <c r="BA17" s="44" t="n">
+      <c r="BA17" s="48" t="n">
         <v>37.4942</v>
       </c>
-      <c r="BB17" s="44" t="n">
+      <c r="BB17" s="48" t="n">
         <v>36.7076</v>
       </c>
-      <c r="BC17" s="44" t="n">
+      <c r="BC17" s="48" t="n">
         <v>37.0484</v>
       </c>
-      <c r="BD17" s="44" t="n">
+      <c r="BD17" s="48" t="n">
         <v>35.4488</v>
       </c>
-      <c r="BE17" s="44" t="n">
+      <c r="BE17" s="48" t="n">
         <v>33.163</v>
       </c>
-      <c r="BF17" s="44" t="n">
+      <c r="BF17" s="48" t="n">
         <v>28.927</v>
       </c>
-      <c r="BG17" s="44" t="n">
+      <c r="BG17" s="48" t="n">
         <v>34.4031</v>
       </c>
-      <c r="BH17" s="44" t="n">
+      <c r="BH17" s="48" t="n">
         <v>30.9093</v>
       </c>
-      <c r="BI17" s="44" t="n">
+      <c r="BI17" s="48" t="n">
         <v>28.3478</v>
       </c>
-      <c r="BJ17" s="44" t="n">
+      <c r="BJ17" s="48" t="n">
         <v>27.3017</v>
       </c>
-      <c r="BK17" s="44" t="n">
+      <c r="BK17" s="48" t="n">
         <v>28.5218</v>
       </c>
-      <c r="BL17" s="44" t="n">
+      <c r="BL17" s="48" t="n">
         <v>20.9163</v>
       </c>
-      <c r="BM17" s="44" t="n">
+      <c r="BM17" s="48" t="n">
         <v>14.9332</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n">
+      <c r="B18" s="48" t="n">
         <v>61.051</v>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="48" t="n">
         <v>65.9915</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="48" t="n">
         <v>65.3438</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="48" t="n">
         <v>64.90349999999999</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="48" t="n">
         <v>64.2099</v>
       </c>
-      <c r="G18" s="44" t="n">
+      <c r="G18" s="48" t="n">
         <v>63.996</v>
       </c>
-      <c r="H18" s="44" t="n">
+      <c r="H18" s="48" t="n">
         <v>61.4272</v>
       </c>
-      <c r="I18" s="44" t="n">
+      <c r="I18" s="48" t="n">
         <v>61.0476</v>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J18" s="48" t="n">
         <v>61.1191</v>
       </c>
-      <c r="K18" s="44" t="n">
+      <c r="K18" s="48" t="n">
         <v>58.3103</v>
       </c>
-      <c r="L18" s="44" t="n">
+      <c r="L18" s="48" t="n">
         <v>59.485</v>
       </c>
-      <c r="M18" s="44" t="n">
+      <c r="M18" s="48" t="n">
         <v>58.525</v>
       </c>
-      <c r="N18" s="44" t="n">
+      <c r="N18" s="48" t="n">
         <v>56.8878</v>
       </c>
-      <c r="O18" s="44" t="n">
+      <c r="O18" s="48" t="n">
         <v>59.8305</v>
       </c>
-      <c r="P18" s="44" t="n">
+      <c r="P18" s="48" t="n">
         <v>55.7392</v>
       </c>
-      <c r="Q18" s="44" t="n">
+      <c r="Q18" s="48" t="n">
         <v>56.7919</v>
       </c>
-      <c r="R18" s="44" t="n">
+      <c r="R18" s="48" t="n">
         <v>57.3426</v>
       </c>
-      <c r="S18" s="44" t="n">
+      <c r="S18" s="48" t="n">
         <v>56.5631</v>
       </c>
-      <c r="T18" s="44" t="n">
+      <c r="T18" s="48" t="n">
         <v>54.974</v>
       </c>
-      <c r="U18" s="44" t="n">
+      <c r="U18" s="48" t="n">
         <v>60.2635</v>
       </c>
-      <c r="V18" s="44" t="n">
+      <c r="V18" s="48" t="n">
         <v>54.9503</v>
       </c>
-      <c r="W18" s="44" t="n">
+      <c r="W18" s="48" t="n">
         <v>53.5313</v>
       </c>
-      <c r="X18" s="44" t="n">
+      <c r="X18" s="48" t="n">
         <v>52.6239</v>
       </c>
-      <c r="Y18" s="44" t="n">
+      <c r="Y18" s="48" t="n">
         <v>51.773</v>
       </c>
-      <c r="Z18" s="44" t="n">
+      <c r="Z18" s="48" t="n">
         <v>54.0988</v>
       </c>
-      <c r="AA18" s="44" t="n">
+      <c r="AA18" s="48" t="n">
         <v>52.3145</v>
       </c>
-      <c r="AB18" s="44" t="n">
+      <c r="AB18" s="48" t="n">
         <v>52.9994</v>
       </c>
-      <c r="AC18" s="44" t="n">
+      <c r="AC18" s="48" t="n">
         <v>50.3962</v>
       </c>
-      <c r="AD18" s="44" t="n">
+      <c r="AD18" s="48" t="n">
         <v>45.7921</v>
       </c>
-      <c r="AE18" s="44" t="n">
+      <c r="AE18" s="48" t="n">
         <v>45.639</v>
       </c>
-      <c r="AF18" s="44" t="n">
+      <c r="AF18" s="48" t="n">
         <v>48.6047</v>
       </c>
-      <c r="AG18" s="44" t="n">
+      <c r="AG18" s="48" t="n">
         <v>48.8859</v>
       </c>
-      <c r="AH18" s="44" t="n">
+      <c r="AH18" s="48" t="n">
         <v>46.6597</v>
       </c>
-      <c r="AI18" s="44" t="n">
+      <c r="AI18" s="48" t="n">
         <v>45.9049</v>
       </c>
-      <c r="AJ18" s="44" t="n">
+      <c r="AJ18" s="48" t="n">
         <v>46.8811</v>
       </c>
-      <c r="AK18" s="44" t="n">
+      <c r="AK18" s="48" t="n">
         <v>46.8807</v>
       </c>
-      <c r="AL18" s="44" t="n">
+      <c r="AL18" s="48" t="n">
         <v>47.8809</v>
       </c>
-      <c r="AM18" s="44" t="n">
+      <c r="AM18" s="48" t="n">
         <v>46.8539</v>
       </c>
-      <c r="AN18" s="44" t="n">
+      <c r="AN18" s="48" t="n">
         <v>44.645</v>
       </c>
-      <c r="AO18" s="44" t="n">
+      <c r="AO18" s="48" t="n">
         <v>45.4796</v>
       </c>
-      <c r="AP18" s="44" t="n">
+      <c r="AP18" s="48" t="n">
         <v>46.3525</v>
       </c>
-      <c r="AQ18" s="44" t="n">
+      <c r="AQ18" s="48" t="n">
         <v>44.354</v>
       </c>
-      <c r="AR18" s="44" t="n">
+      <c r="AR18" s="48" t="n">
         <v>49.9253</v>
       </c>
-      <c r="AS18" s="44" t="n">
+      <c r="AS18" s="48" t="n">
         <v>42.9438</v>
       </c>
-      <c r="AT18" s="44" t="n">
+      <c r="AT18" s="48" t="n">
         <v>41.4794</v>
       </c>
-      <c r="AU18" s="44" t="n">
+      <c r="AU18" s="48" t="n">
         <v>43.1469</v>
       </c>
-      <c r="AV18" s="44" t="n">
+      <c r="AV18" s="48" t="n">
         <v>40.0293</v>
       </c>
-      <c r="AW18" s="44" t="n">
+      <c r="AW18" s="48" t="n">
         <v>42.9168</v>
       </c>
-      <c r="AX18" s="44" t="n">
+      <c r="AX18" s="48" t="n">
         <v>42.6237</v>
       </c>
-      <c r="AY18" s="44" t="n">
+      <c r="AY18" s="48" t="n">
         <v>36.9106</v>
       </c>
-      <c r="AZ18" s="44" t="n">
+      <c r="AZ18" s="48" t="n">
         <v>40.4246</v>
       </c>
-      <c r="BA18" s="44" t="n">
+      <c r="BA18" s="48" t="n">
         <v>37.5141</v>
       </c>
-      <c r="BB18" s="44" t="n">
+      <c r="BB18" s="48" t="n">
         <v>36.581</v>
       </c>
-      <c r="BC18" s="44" t="n">
+      <c r="BC18" s="48" t="n">
         <v>36.4923</v>
       </c>
-      <c r="BD18" s="44" t="n">
+      <c r="BD18" s="48" t="n">
         <v>35.8977</v>
       </c>
-      <c r="BE18" s="44" t="n">
+      <c r="BE18" s="48" t="n">
         <v>32.5199</v>
       </c>
-      <c r="BF18" s="44" t="n">
+      <c r="BF18" s="48" t="n">
         <v>29.9036</v>
       </c>
-      <c r="BG18" s="44" t="n">
+      <c r="BG18" s="48" t="n">
         <v>33.4561</v>
       </c>
-      <c r="BH18" s="44" t="n">
+      <c r="BH18" s="48" t="n">
         <v>30.7169</v>
       </c>
-      <c r="BI18" s="44" t="n">
+      <c r="BI18" s="48" t="n">
         <v>28.4053</v>
       </c>
-      <c r="BJ18" s="44" t="n">
+      <c r="BJ18" s="48" t="n">
         <v>26.8258</v>
       </c>
-      <c r="BK18" s="44" t="n">
+      <c r="BK18" s="48" t="n">
         <v>28.8288</v>
       </c>
-      <c r="BL18" s="44" t="n">
+      <c r="BL18" s="48" t="n">
         <v>20.9256</v>
       </c>
-      <c r="BM18" s="44" t="n">
+      <c r="BM18" s="48" t="n">
         <v>16.5031</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B19" s="44" t="n">
+      <c r="B19" s="48" t="n">
         <v>66.7509</v>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="48" t="n">
         <v>65.9791</v>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="48" t="n">
         <v>65.9628</v>
       </c>
-      <c r="E19" s="44" t="n">
+      <c r="E19" s="48" t="n">
         <v>65.5505</v>
       </c>
-      <c r="F19" s="44" t="n">
+      <c r="F19" s="48" t="n">
         <v>64.79470000000001</v>
       </c>
-      <c r="G19" s="44" t="n">
+      <c r="G19" s="48" t="n">
         <v>64.4178</v>
       </c>
-      <c r="H19" s="44" t="n">
+      <c r="H19" s="48" t="n">
         <v>61.8966</v>
       </c>
-      <c r="I19" s="44" t="n">
+      <c r="I19" s="48" t="n">
         <v>61.1832</v>
       </c>
-      <c r="J19" s="44" t="n">
+      <c r="J19" s="48" t="n">
         <v>60.9784</v>
       </c>
-      <c r="K19" s="44" t="n">
+      <c r="K19" s="48" t="n">
         <v>60.0808</v>
       </c>
-      <c r="L19" s="44" t="n">
+      <c r="L19" s="48" t="n">
         <v>59.9366</v>
       </c>
-      <c r="M19" s="44" t="n">
+      <c r="M19" s="48" t="n">
         <v>59.5883</v>
       </c>
-      <c r="N19" s="44" t="n">
+      <c r="N19" s="48" t="n">
         <v>59.4197</v>
       </c>
-      <c r="O19" s="44" t="n">
+      <c r="O19" s="48" t="n">
         <v>59.3939</v>
       </c>
-      <c r="P19" s="44" t="n">
+      <c r="P19" s="48" t="n">
         <v>58.8976</v>
       </c>
-      <c r="Q19" s="44" t="n">
+      <c r="Q19" s="48" t="n">
         <v>58.5181</v>
       </c>
-      <c r="R19" s="44" t="n">
+      <c r="R19" s="48" t="n">
         <v>57.6205</v>
       </c>
-      <c r="S19" s="44" t="n">
+      <c r="S19" s="48" t="n">
         <v>56.6433</v>
       </c>
-      <c r="T19" s="44" t="n">
+      <c r="T19" s="48" t="n">
         <v>56.5263</v>
       </c>
-      <c r="U19" s="44" t="n">
+      <c r="U19" s="48" t="n">
         <v>56.3381</v>
       </c>
-      <c r="V19" s="44" t="n">
+      <c r="V19" s="48" t="n">
         <v>55.3047</v>
       </c>
-      <c r="W19" s="44" t="n">
+      <c r="W19" s="48" t="n">
         <v>54.3613</v>
       </c>
-      <c r="X19" s="44" t="n">
+      <c r="X19" s="48" t="n">
         <v>53.9287</v>
       </c>
-      <c r="Y19" s="44" t="n">
+      <c r="Y19" s="48" t="n">
         <v>53.4325</v>
       </c>
-      <c r="Z19" s="44" t="n">
+      <c r="Z19" s="48" t="n">
         <v>53.3413</v>
       </c>
-      <c r="AA19" s="44" t="n">
+      <c r="AA19" s="48" t="n">
         <v>53.0096</v>
       </c>
-      <c r="AB19" s="44" t="n">
+      <c r="AB19" s="48" t="n">
         <v>52.5477</v>
       </c>
-      <c r="AC19" s="44" t="n">
+      <c r="AC19" s="48" t="n">
         <v>50.3891</v>
       </c>
-      <c r="AD19" s="44" t="n">
+      <c r="AD19" s="48" t="n">
         <v>49.3256</v>
       </c>
-      <c r="AE19" s="44" t="n">
+      <c r="AE19" s="48" t="n">
         <v>48.4571</v>
       </c>
-      <c r="AF19" s="44" t="n">
+      <c r="AF19" s="48" t="n">
         <v>48.4517</v>
       </c>
-      <c r="AG19" s="44" t="n">
+      <c r="AG19" s="48" t="n">
         <v>48.4476</v>
       </c>
-      <c r="AH19" s="44" t="n">
+      <c r="AH19" s="48" t="n">
         <v>48.3845</v>
       </c>
-      <c r="AI19" s="44" t="n">
+      <c r="AI19" s="48" t="n">
         <v>48.3388</v>
       </c>
-      <c r="AJ19" s="44" t="n">
+      <c r="AJ19" s="48" t="n">
         <v>47.7865</v>
       </c>
-      <c r="AK19" s="44" t="n">
+      <c r="AK19" s="48" t="n">
         <v>47.3434</v>
       </c>
-      <c r="AL19" s="44" t="n">
+      <c r="AL19" s="48" t="n">
         <v>47.2444</v>
       </c>
-      <c r="AM19" s="44" t="n">
+      <c r="AM19" s="48" t="n">
         <v>46.9993</v>
       </c>
-      <c r="AN19" s="44" t="n">
+      <c r="AN19" s="48" t="n">
         <v>46.1864</v>
       </c>
-      <c r="AO19" s="44" t="n">
+      <c r="AO19" s="48" t="n">
         <v>45.7889</v>
       </c>
-      <c r="AP19" s="44" t="n">
+      <c r="AP19" s="48" t="n">
         <v>45.2849</v>
       </c>
-      <c r="AQ19" s="44" t="n">
+      <c r="AQ19" s="48" t="n">
         <v>45.2261</v>
       </c>
-      <c r="AR19" s="44" t="n">
+      <c r="AR19" s="48" t="n">
         <v>44.8209</v>
       </c>
-      <c r="AS19" s="44" t="n">
+      <c r="AS19" s="48" t="n">
         <v>44.5903</v>
       </c>
-      <c r="AT19" s="44" t="n">
+      <c r="AT19" s="48" t="n">
         <v>43.128</v>
       </c>
-      <c r="AU19" s="44" t="n">
+      <c r="AU19" s="48" t="n">
         <v>42.3919</v>
       </c>
-      <c r="AV19" s="44" t="n">
+      <c r="AV19" s="48" t="n">
         <v>42.0426</v>
       </c>
-      <c r="AW19" s="44" t="n">
+      <c r="AW19" s="48" t="n">
         <v>41.4853</v>
       </c>
-      <c r="AX19" s="44" t="n">
+      <c r="AX19" s="48" t="n">
         <v>40.8302</v>
       </c>
-      <c r="AY19" s="44" t="n">
+      <c r="AY19" s="48" t="n">
         <v>40.1833</v>
       </c>
-      <c r="AZ19" s="44" t="n">
+      <c r="AZ19" s="48" t="n">
         <v>39.2626</v>
       </c>
-      <c r="BA19" s="44" t="n">
+      <c r="BA19" s="48" t="n">
         <v>38.3425</v>
       </c>
-      <c r="BB19" s="44" t="n">
+      <c r="BB19" s="48" t="n">
         <v>36.6697</v>
       </c>
-      <c r="BC19" s="44" t="n">
+      <c r="BC19" s="48" t="n">
         <v>36.4079</v>
       </c>
-      <c r="BD19" s="44" t="n">
+      <c r="BD19" s="48" t="n">
         <v>34.7188</v>
       </c>
-      <c r="BE19" s="44" t="n">
+      <c r="BE19" s="48" t="n">
         <v>33.7003</v>
       </c>
-      <c r="BF19" s="44" t="n">
+      <c r="BF19" s="48" t="n">
         <v>32.5402</v>
       </c>
-      <c r="BG19" s="44" t="n">
+      <c r="BG19" s="48" t="n">
         <v>31.8337</v>
       </c>
-      <c r="BH19" s="44" t="n">
+      <c r="BH19" s="48" t="n">
         <v>31.669</v>
       </c>
-      <c r="BI19" s="44" t="n">
+      <c r="BI19" s="48" t="n">
         <v>30.6285</v>
       </c>
-      <c r="BJ19" s="44" t="n">
+      <c r="BJ19" s="48" t="n">
         <v>29.7597</v>
       </c>
-      <c r="BK19" s="44" t="n">
+      <c r="BK19" s="48" t="n">
         <v>28.6254</v>
       </c>
-      <c r="BL19" s="44" t="n">
+      <c r="BL19" s="48" t="n">
         <v>22.3108</v>
       </c>
-      <c r="BM19" s="44" t="n">
+      <c r="BM19" s="48" t="n">
         <v>16.3398</v>
       </c>
     </row>
@@ -21233,7 +24669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53438,7 +56874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53452,7 +56888,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>US Stock Watchlist — 4-Pillar Quantitative Score (lean standard)</t>
         </is>
@@ -53464,7 +56900,7 @@
       <c r="B2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>Score = Momentum/25 + Risk/25 + Fundamentals/25 + Valuation/25 (0-100)</t>
         </is>
@@ -53472,7 +56908,7 @@
       <c r="B3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ETFs &amp; indices: scored on Momentum + Risk only, rescaled to 100</t>
         </is>
@@ -53480,7 +56916,7 @@
       <c r="B4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Each sub-metric uses an absolute linear ramp; pillars are rescaled over available sub-metrics when data is missing</t>
         </is>
@@ -53612,7 +57048,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>RISK (25, lower risk = higher score)</t>
         </is>
@@ -53680,7 +57116,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>FUNDAMENTALS (25)</t>
         </is>
@@ -53784,7 +57220,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="46" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>VALUATION (25, cheaper = higher score)</t>
         </is>
@@ -53856,7 +57292,7 @@
       <c r="B38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>SIGNALS</t>
         </is>
@@ -53916,7 +57352,7 @@
       <c r="B44" s="1" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>BACKTEST (sheet: Backtest)</t>
         </is>
@@ -53976,7 +57412,7 @@
       <c r="B50" s="1" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>CORRELATION (sheet: Correlation)</t>
         </is>
@@ -54024,7 +57460,7 @@
       <c r="B55" s="1" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="50" t="inlineStr">
         <is>
           <t>Data: Yahoo Finance (daily prices 1Y, fundamentals snapshot). Not investment advice.</t>
         </is>
